--- a/site/exports/zju-ic-manufacturing.xlsx
+++ b/site/exports/zju-ic-manufacturing.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rdc485061c41d4562"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Rd38034011a4b46fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rd823ed9cbacc46e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Re7296c7587674d31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R46f2fee98bab47e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R2ee17c10119f4d8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R098d587d39d54d39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Ree2f66bd3855443e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Rb4134934d59142e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R0f1e9728d7734aad"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T10_0" displayName="T10_0" ref="A1:K4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T10_0" displayName="T10_0" ref="A1:K10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T10_1" displayName="T10_1" ref="A1:S15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T10_1" displayName="T10_1" ref="A1:S50" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -185,7 +185,27 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T10_4" displayName="T10_4" ref="A1:G11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T10_3" displayName="T10_3" ref="A1:L5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="12">
+    <x:tableColumn id="1" name="姓名"/>
+    <x:tableColumn id="2" name="标题"/>
+    <x:tableColumn id="3" name="年份"/>
+    <x:tableColumn id="4" name="DOI"/>
+    <x:tableColumn id="5" name="链接"/>
+    <x:tableColumn id="6" name="类型"/>
+    <x:tableColumn id="7" name="收录来源"/>
+    <x:tableColumn id="8" name="作者归属依据"/>
+    <x:tableColumn id="9" name="链接核验范围"/>
+    <x:tableColumn id="10" name="备注"/>
+    <x:tableColumn id="11" name="所属学校ID"/>
+    <x:tableColumn id="12" name="所属学校"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T10_4" displayName="T10_4" ref="A1:G38" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -541,10 +561,208 @@
         <x:v>浙江大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="5" ht="64" customHeight="1">
+      <x:c r="A5" s="6" t="str">
+        <x:v>程志渊</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="str">
+        <x:v>集成电路学院·先进集成电路制造技术研究所</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="str">
+        <x:v>http://mypage.zju.edu.cn/zcheng</x:v>
+      </x:c>
+      <x:c r="E5" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="str">
+        <x:v>官方个人主页timeout/503，未取得本人完整正文；学士毕业年、哈佛年月、各阶段导师未核。；已读校友文称MIT材料系导师但未给姓名，不能猜导师。；精选个人论文未核，不以团队百篇总量代替。</x:v>
+      </x:c>
+      <x:c r="G5" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H5" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I5" s="6" t="str"/>
+      <x:c r="J5" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="K5" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="64" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>卓成</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="str">
+        <x:v>集成电路学院·先进集成电路制造技术研究所</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/chengzhuo</x:v>
+      </x:c>
+      <x:c r="E6" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="str">
+        <x:v>个人主页403，停止；当前名录百人研究员与副院长职务并列，不推教授晋升日期。；博士论文直接429，只能读索引；委员会Chair与答辩Sponsored by均非独立导师明确表述，本轮不建师承。；学历具体专业、起始年待核；博士年份差异保留。</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I6" s="6" t="str"/>
+      <x:c r="J6" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="K6" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="64" customHeight="1">
+      <x:c r="A7" s="6" t="str">
+        <x:v>曹子峥</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="str">
+        <x:v>集成电路学院·先进集成电路制造技术研究所</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/zzcao</x:v>
+      </x:c>
+      <x:c r="E7" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F7" s="6" t="str">
+        <x:v>官方主页只读头部，后续本地请求403停止。；浙大招聘已确认埃因霍温研究所职业联系；TU/e同名旧论文的具体学历及导师身份链尚未独立完成，本轮只增已核职业信息，不冒填授位学校。</x:v>
+      </x:c>
+      <x:c r="G7" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H7" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I7" s="6" t="str"/>
+      <x:c r="J7" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="K7" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="64" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>韩雁</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str">
+        <x:v>集成电路学院·先进集成电路制造技术研究所</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/2025/0115/c81879a3012574/page.htm</x:v>
+      </x:c>
+      <x:c r="E8" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="str">
+        <x:v>硕博授位学校、专业、国家洲及导师未明确；1982毕业阶段未写。；官网列145篇论文总量而无逐篇书目，本轮不造论文记录；历任行政岗未标年月，不作为当前岗位。</x:v>
+      </x:c>
+      <x:c r="G8" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H8" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I8" s="6" t="str"/>
+      <x:c r="J8" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="K8" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="64" customHeight="1">
+      <x:c r="A9" s="6" t="str">
+        <x:v>张睿</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="str">
+        <x:v>集成电路学院·先进集成电路制造技术研究所</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/0012183</x:v>
+      </x:c>
+      <x:c r="E9" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F9" s="6" t="str">
+        <x:v>博士导师及各学位起始年份未核；正文403不进一步请求。；现行教授与2021副教授是不同时间点，不推晋升年。</x:v>
+      </x:c>
+      <x:c r="G9" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H9" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I9" s="6" t="str"/>
+      <x:c r="J9" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="K9" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="64" customHeight="1">
+      <x:c r="A10" s="6" t="str">
+        <x:v>程然</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="str">
+        <x:v>集成电路学院·先进集成电路制造技术研究所</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/chengran</x:v>
+      </x:c>
+      <x:c r="E10" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F10" s="6" t="str">
+        <x:v>本人主页403停止；已由独立出版者正文核实学士及博士授位，不代表完整本人网页已读取。；教育起始时间、硕士经历是否存在及导师未知；未披露不等不存在。；院系申报教授公示不证已聘教授，继续保留现行名录副教授。</x:v>
+      </x:c>
+      <x:c r="G10" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H10" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I10" s="6" t="str"/>
+      <x:c r="J10" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="K10" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fac90d3aed04e5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R869e4aa55d05416f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1189,10 +1407,1517 @@
         <x:v>浙江大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="16" ht="64" customHeight="1">
+      <x:c r="A16" s="6" t="str">
+        <x:v>程志渊</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C16" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D16" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E16" s="6" t="str">
+        <x:v>1985</x:v>
+      </x:c>
+      <x:c r="F16" s="6" t="str"/>
+      <x:c r="G16" s="6" t="str">
+        <x:v>电子工程</x:v>
+      </x:c>
+      <x:c r="H16" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I16" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J16" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K16" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L16" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M16" s="7" t="str"/>
+      <x:c r="N16" s="6" t="str"/>
+      <x:c r="O16" s="6" t="str">
+        <x:v>中国科协科创中国本人职业简介明确清华学士；1985入学另由清华校友会记录，不猜毕业年。</x:v>
+      </x:c>
+      <x:c r="P16" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q16" s="6" t="str">
+        <x:v>https://www.kczg.org.cn/xuezhe/details?id=403894</x:v>
+      </x:c>
+      <x:c r="R16" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S16" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="64" customHeight="1">
+      <x:c r="A17" s="6" t="str">
+        <x:v>程志渊</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C17" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D17" s="6" t="str">
+        <x:v>新加坡国立大学</x:v>
+      </x:c>
+      <x:c r="E17" s="6" t="str">
+        <x:v>1995</x:v>
+      </x:c>
+      <x:c r="F17" s="6" t="str">
+        <x:v>1999</x:v>
+      </x:c>
+      <x:c r="G17" s="6" t="str">
+        <x:v>电子工程</x:v>
+      </x:c>
+      <x:c r="H17" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="I17" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="J17" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K17" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L17" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M17" s="7" t="str"/>
+      <x:c r="N17" s="6" t="str"/>
+      <x:c r="O17" s="6" t="str">
+        <x:v>清华校友会明确1995开始攻读、1999获博士。独立评审赞语“足以获得两个博士”不是第二学位。</x:v>
+      </x:c>
+      <x:c r="P17" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q17" s="6" t="str">
+        <x:v>https://www.tsinghua.org.cn/info/1951/18473.htm</x:v>
+      </x:c>
+      <x:c r="R17" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S17" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="64" customHeight="1">
+      <x:c r="A18" s="6" t="str">
+        <x:v>程志渊</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C18" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D18" s="6" t="str">
+        <x:v>哈佛大学</x:v>
+      </x:c>
+      <x:c r="E18" s="6" t="str"/>
+      <x:c r="F18" s="6" t="str"/>
+      <x:c r="G18" s="6" t="str">
+        <x:v>公共管理</x:v>
+      </x:c>
+      <x:c r="H18" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="I18" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="J18" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K18" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L18" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M18" s="7" t="str"/>
+      <x:c r="N18" s="6" t="str"/>
+      <x:c r="O18" s="6" t="str">
+        <x:v>肯尼迪政府学院公共管理硕士，时间未知；发生在博士后阶段附近但不据叙述顺序造年月。</x:v>
+      </x:c>
+      <x:c r="P18" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q18" s="6" t="str">
+        <x:v>https://www.tsinghua.org.cn/info/1951/18473.htm</x:v>
+      </x:c>
+      <x:c r="R18" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S18" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="64" customHeight="1">
+      <x:c r="A19" s="6" t="str">
+        <x:v>程志渊</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D19" s="6" t="str">
+        <x:v>浙江大学集成电路学院</x:v>
+      </x:c>
+      <x:c r="E19" s="6" t="str"/>
+      <x:c r="F19" s="6" t="str"/>
+      <x:c r="G19" s="6" t="str"/>
+      <x:c r="H19" s="6" t="str"/>
+      <x:c r="I19" s="6" t="str"/>
+      <x:c r="J19" s="6" t="str"/>
+      <x:c r="K19" s="6" t="str"/>
+      <x:c r="L19" s="6" t="str"/>
+      <x:c r="M19" s="7" t="str"/>
+      <x:c r="N19" s="6" t="str"/>
+      <x:c r="O19" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P19" s="6" t="str"/>
+      <x:c r="Q19" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/jcdlxjzzjsyjs/</x:v>
+      </x:c>
+      <x:c r="R19" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S19" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="64" customHeight="1">
+      <x:c r="A20" s="6" t="str">
+        <x:v>程志渊</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C20" s="6" t="str">
+        <x:v>博士后</x:v>
+      </x:c>
+      <x:c r="D20" s="6" t="str">
+        <x:v>麻省理工学院材料系与电子系</x:v>
+      </x:c>
+      <x:c r="E20" s="6" t="str">
+        <x:v>2000</x:v>
+      </x:c>
+      <x:c r="F20" s="6" t="str">
+        <x:v>2003</x:v>
+      </x:c>
+      <x:c r="G20" s="6" t="str"/>
+      <x:c r="H20" s="6" t="str"/>
+      <x:c r="I20" s="6" t="str"/>
+      <x:c r="J20" s="6" t="str"/>
+      <x:c r="K20" s="6" t="str"/>
+      <x:c r="L20" s="6" t="str"/>
+      <x:c r="M20" s="7" t="str"/>
+      <x:c r="N20" s="6" t="str"/>
+      <x:c r="O20" s="6" t="str">
+        <x:v>非授位研究岗位。</x:v>
+      </x:c>
+      <x:c r="P20" s="6" t="str"/>
+      <x:c r="Q20" s="6" t="str">
+        <x:v>https://www.tsinghua.org.cn/info/1951/18473.htm</x:v>
+      </x:c>
+      <x:c r="R20" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S20" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="64" customHeight="1">
+      <x:c r="A21" s="6" t="str">
+        <x:v>程志渊</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C21" s="6" t="str">
+        <x:v>科研及产业工作</x:v>
+      </x:c>
+      <x:c r="D21" s="6" t="str">
+        <x:v>美国多家科技公司（未逐家核定）</x:v>
+      </x:c>
+      <x:c r="E21" s="6" t="str">
+        <x:v>2003</x:v>
+      </x:c>
+      <x:c r="F21" s="6" t="str">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="G21" s="6" t="str"/>
+      <x:c r="H21" s="6" t="str"/>
+      <x:c r="I21" s="6" t="str"/>
+      <x:c r="J21" s="6" t="str"/>
+      <x:c r="K21" s="6" t="str"/>
+      <x:c r="L21" s="6" t="str"/>
+      <x:c r="M21" s="7" t="str"/>
+      <x:c r="N21" s="6" t="str"/>
+      <x:c r="O21" s="6" t="str"/>
+      <x:c r="P21" s="6" t="str"/>
+      <x:c r="Q21" s="6" t="str">
+        <x:v>https://www.kczg.org.cn/xuezhe/details?id=403894</x:v>
+      </x:c>
+      <x:c r="R21" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S21" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="64" customHeight="1">
+      <x:c r="A22" s="6" t="str">
+        <x:v>程志渊</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C22" s="6" t="str">
+        <x:v>教授（先后信电、微纳电子学院）</x:v>
+      </x:c>
+      <x:c r="D22" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+      <x:c r="E22" s="6" t="str">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="F22" s="6" t="str"/>
+      <x:c r="G22" s="6" t="str"/>
+      <x:c r="H22" s="6" t="str"/>
+      <x:c r="I22" s="6" t="str"/>
+      <x:c r="J22" s="6" t="str"/>
+      <x:c r="K22" s="6" t="str"/>
+      <x:c r="L22" s="6" t="str"/>
+      <x:c r="M22" s="7" t="str"/>
+      <x:c r="N22" s="6" t="str"/>
+      <x:c r="O22" s="6" t="str">
+        <x:v>加入浙大时间2014，具体各学院任期未细分。</x:v>
+      </x:c>
+      <x:c r="P22" s="6" t="str"/>
+      <x:c r="Q22" s="6" t="str">
+        <x:v>https://www.kczg.org.cn/xuezhe/details?id=403894</x:v>
+      </x:c>
+      <x:c r="R22" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S22" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="64" customHeight="1">
+      <x:c r="A23" s="6" t="str">
+        <x:v>卓成</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C23" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D23" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+      <x:c r="E23" s="6" t="str"/>
+      <x:c r="F23" s="6" t="str">
+        <x:v>2005</x:v>
+      </x:c>
+      <x:c r="G23" s="6" t="str"/>
+      <x:c r="H23" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I23" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J23" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K23" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L23" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M23" s="7" t="str"/>
+      <x:c r="N23" s="6" t="str"/>
+      <x:c r="O23" s="6" t="str">
+        <x:v>峰会官方嘉宾简介明确获学位；前两年可核，博士年份有2010简历/2011论文元数据差异，日期暂空不混答辩与授位。</x:v>
+      </x:c>
+      <x:c r="P23" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q23" s="6" t="str">
+        <x:v>https://www.szics.net/guests/124/</x:v>
+      </x:c>
+      <x:c r="R23" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S23" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="64" customHeight="1">
+      <x:c r="A24" s="6" t="str">
+        <x:v>卓成</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C24" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D24" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+      <x:c r="E24" s="6" t="str"/>
+      <x:c r="F24" s="6" t="str">
+        <x:v>2007</x:v>
+      </x:c>
+      <x:c r="G24" s="6" t="str"/>
+      <x:c r="H24" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I24" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J24" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K24" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L24" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M24" s="7" t="str"/>
+      <x:c r="N24" s="6" t="str"/>
+      <x:c r="O24" s="6" t="str">
+        <x:v>峰会官方嘉宾简介明确获学位；前两年可核，博士年份有2010简历/2011论文元数据差异，日期暂空不混答辩与授位。</x:v>
+      </x:c>
+      <x:c r="P24" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q24" s="6" t="str">
+        <x:v>https://www.szics.net/guests/124/</x:v>
+      </x:c>
+      <x:c r="R24" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S24" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="64" customHeight="1">
+      <x:c r="A25" s="6" t="str">
+        <x:v>卓成</x:v>
+      </x:c>
+      <x:c r="B25" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C25" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D25" s="6" t="str">
+        <x:v>密歇根大学安娜堡分校</x:v>
+      </x:c>
+      <x:c r="E25" s="6" t="str"/>
+      <x:c r="F25" s="6" t="str"/>
+      <x:c r="G25" s="6" t="str"/>
+      <x:c r="H25" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="I25" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="J25" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K25" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L25" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M25" s="7" t="str"/>
+      <x:c r="N25" s="6" t="str"/>
+      <x:c r="O25" s="6" t="str">
+        <x:v>峰会官方嘉宾简介明确获学位；前两年可核，博士年份有2010简历/2011论文元数据差异，日期暂空不混答辩与授位。</x:v>
+      </x:c>
+      <x:c r="P25" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q25" s="6" t="str">
+        <x:v>https://www.szics.net/guests/124/</x:v>
+      </x:c>
+      <x:c r="R25" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S25" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="64" customHeight="1">
+      <x:c r="A26" s="6" t="str">
+        <x:v>卓成</x:v>
+      </x:c>
+      <x:c r="B26" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C26" s="6" t="str">
+        <x:v>百人计划研究员</x:v>
+      </x:c>
+      <x:c r="D26" s="6" t="str">
+        <x:v>浙江大学集成电路学院</x:v>
+      </x:c>
+      <x:c r="E26" s="6" t="str"/>
+      <x:c r="F26" s="6" t="str"/>
+      <x:c r="G26" s="6" t="str"/>
+      <x:c r="H26" s="6" t="str"/>
+      <x:c r="I26" s="6" t="str"/>
+      <x:c r="J26" s="6" t="str"/>
+      <x:c r="K26" s="6" t="str"/>
+      <x:c r="L26" s="6" t="str"/>
+      <x:c r="M26" s="7" t="str"/>
+      <x:c r="N26" s="6" t="str"/>
+      <x:c r="O26" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P26" s="6" t="str"/>
+      <x:c r="Q26" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/jcdlxjzzjsyjs/</x:v>
+      </x:c>
+      <x:c r="R26" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S26" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="64" customHeight="1">
+      <x:c r="A27" s="6" t="str">
+        <x:v>卓成</x:v>
+      </x:c>
+      <x:c r="B27" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C27" s="6" t="str">
+        <x:v>科研工作（具体岗位未列）</x:v>
+      </x:c>
+      <x:c r="D27" s="6" t="str">
+        <x:v>英特尔公司</x:v>
+      </x:c>
+      <x:c r="E27" s="6" t="str">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="F27" s="6" t="str">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="G27" s="6" t="str"/>
+      <x:c r="H27" s="6" t="str"/>
+      <x:c r="I27" s="6" t="str"/>
+      <x:c r="J27" s="6" t="str"/>
+      <x:c r="K27" s="6" t="str"/>
+      <x:c r="L27" s="6" t="str"/>
+      <x:c r="M27" s="7" t="str"/>
+      <x:c r="N27" s="6" t="str"/>
+      <x:c r="O27" s="6" t="str"/>
+      <x:c r="P27" s="6" t="str"/>
+      <x:c r="Q27" s="6" t="str">
+        <x:v>https://www.szics.net/guests/124/</x:v>
+      </x:c>
+      <x:c r="R27" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S27" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="64" customHeight="1">
+      <x:c r="A28" s="6" t="str">
+        <x:v>卓成</x:v>
+      </x:c>
+      <x:c r="B28" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C28" s="6" t="str">
+        <x:v>教师</x:v>
+      </x:c>
+      <x:c r="D28" s="6" t="str">
+        <x:v>浙江大学信息与电子工程学院</x:v>
+      </x:c>
+      <x:c r="E28" s="6" t="str">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="F28" s="6" t="str"/>
+      <x:c r="G28" s="6" t="str"/>
+      <x:c r="H28" s="6" t="str"/>
+      <x:c r="I28" s="6" t="str"/>
+      <x:c r="J28" s="6" t="str"/>
+      <x:c r="K28" s="6" t="str"/>
+      <x:c r="L28" s="6" t="str"/>
+      <x:c r="M28" s="7" t="str"/>
+      <x:c r="N28" s="6" t="str"/>
+      <x:c r="O28" s="6" t="str">
+        <x:v>峰会资料发布时的现职单位；现行院校组织另按名录列示。</x:v>
+      </x:c>
+      <x:c r="P28" s="6" t="str"/>
+      <x:c r="Q28" s="6" t="str">
+        <x:v>https://www.szics.net/guests/124/</x:v>
+      </x:c>
+      <x:c r="R28" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S28" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="64" customHeight="1">
+      <x:c r="A29" s="6" t="str">
+        <x:v>卓成</x:v>
+      </x:c>
+      <x:c r="B29" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C29" s="6" t="str">
+        <x:v>客座教授</x:v>
+      </x:c>
+      <x:c r="D29" s="6" t="str">
+        <x:v>大阪大学</x:v>
+      </x:c>
+      <x:c r="E29" s="6" t="str">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="F29" s="6" t="str">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="G29" s="6" t="str"/>
+      <x:c r="H29" s="6" t="str"/>
+      <x:c r="I29" s="6" t="str"/>
+      <x:c r="J29" s="6" t="str"/>
+      <x:c r="K29" s="6" t="str"/>
+      <x:c r="L29" s="6" t="str"/>
+      <x:c r="M29" s="7" t="str"/>
+      <x:c r="N29" s="6" t="str"/>
+      <x:c r="O29" s="6" t="str">
+        <x:v>年度任职陈述，具体月份未披露。</x:v>
+      </x:c>
+      <x:c r="P29" s="6" t="str"/>
+      <x:c r="Q29" s="6" t="str">
+        <x:v>https://www.szics.net/guests/124/</x:v>
+      </x:c>
+      <x:c r="R29" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S29" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="64" customHeight="1">
+      <x:c r="A30" s="6" t="str">
+        <x:v>卓成</x:v>
+      </x:c>
+      <x:c r="B30" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C30" s="6" t="str">
+        <x:v>副院长</x:v>
+      </x:c>
+      <x:c r="D30" s="6" t="str">
+        <x:v>浙江大学集成电路学院</x:v>
+      </x:c>
+      <x:c r="E30" s="6" t="str"/>
+      <x:c r="F30" s="6" t="str"/>
+      <x:c r="G30" s="6" t="str"/>
+      <x:c r="H30" s="6" t="str"/>
+      <x:c r="I30" s="6" t="str"/>
+      <x:c r="J30" s="6" t="str"/>
+      <x:c r="K30" s="6" t="str"/>
+      <x:c r="L30" s="6" t="str"/>
+      <x:c r="M30" s="7" t="str"/>
+      <x:c r="N30" s="6" t="str"/>
+      <x:c r="O30" s="6" t="str">
+        <x:v>2026-05-07学院新闻直接称卓成副院长，未由旧个人主页推定任期。</x:v>
+      </x:c>
+      <x:c r="P30" s="6" t="str"/>
+      <x:c r="Q30" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/2026/0507/c53931a3159480/page.psp</x:v>
+      </x:c>
+      <x:c r="R30" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S30" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="64" customHeight="1">
+      <x:c r="A31" s="6" t="str">
+        <x:v>曹子峥</x:v>
+      </x:c>
+      <x:c r="B31" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C31" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D31" s="6" t="str"/>
+      <x:c r="E31" s="6" t="str"/>
+      <x:c r="F31" s="6" t="str"/>
+      <x:c r="G31" s="6" t="str"/>
+      <x:c r="H31" s="6" t="str"/>
+      <x:c r="I31" s="6" t="str"/>
+      <x:c r="J31" s="6" t="str"/>
+      <x:c r="K31" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L31" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M31" s="7" t="str"/>
+      <x:c r="N31" s="6" t="str"/>
+      <x:c r="O31" s="6" t="str">
+        <x:v>已读官方头部确认博士；具体授位学校和年份需职业身份桥接后再收录。</x:v>
+      </x:c>
+      <x:c r="P31" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q31" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/zzcao</x:v>
+      </x:c>
+      <x:c r="R31" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S31" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="64" customHeight="1">
+      <x:c r="A32" s="6" t="str">
+        <x:v>曹子峥</x:v>
+      </x:c>
+      <x:c r="B32" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C32" s="6" t="str">
+        <x:v>长聘教授、求是特聘教授、博士生导师</x:v>
+      </x:c>
+      <x:c r="D32" s="6" t="str">
+        <x:v>浙江大学集成电路学院</x:v>
+      </x:c>
+      <x:c r="E32" s="6" t="str"/>
+      <x:c r="F32" s="6" t="str"/>
+      <x:c r="G32" s="6" t="str"/>
+      <x:c r="H32" s="6" t="str"/>
+      <x:c r="I32" s="6" t="str"/>
+      <x:c r="J32" s="6" t="str"/>
+      <x:c r="K32" s="6" t="str"/>
+      <x:c r="L32" s="6" t="str"/>
+      <x:c r="M32" s="7" t="str"/>
+      <x:c r="N32" s="6" t="str"/>
+      <x:c r="O32" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P32" s="6" t="str"/>
+      <x:c r="Q32" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/zzcao</x:v>
+      </x:c>
+      <x:c r="R32" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S32" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="64" customHeight="1">
+      <x:c r="A33" s="6" t="str">
+        <x:v>曹子峥</x:v>
+      </x:c>
+      <x:c r="B33" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C33" s="6" t="str">
+        <x:v>副院长（双专）</x:v>
+      </x:c>
+      <x:c r="D33" s="6" t="str">
+        <x:v>浙江大学上海高等研究院</x:v>
+      </x:c>
+      <x:c r="E33" s="6" t="str"/>
+      <x:c r="F33" s="6" t="str"/>
+      <x:c r="G33" s="6" t="str"/>
+      <x:c r="H33" s="6" t="str"/>
+      <x:c r="I33" s="6" t="str"/>
+      <x:c r="J33" s="6" t="str"/>
+      <x:c r="K33" s="6" t="str"/>
+      <x:c r="L33" s="6" t="str"/>
+      <x:c r="M33" s="7" t="str"/>
+      <x:c r="N33" s="6" t="str"/>
+      <x:c r="O33" s="6" t="str"/>
+      <x:c r="P33" s="6" t="str"/>
+      <x:c r="Q33" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/zzcao</x:v>
+      </x:c>
+      <x:c r="R33" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S33" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="64" customHeight="1">
+      <x:c r="A34" s="6" t="str">
+        <x:v>曹子峥</x:v>
+      </x:c>
+      <x:c r="B34" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C34" s="6" t="str">
+        <x:v>曾任副所长、研究员（二级岗）</x:v>
+      </x:c>
+      <x:c r="D34" s="6" t="str">
+        <x:v>鹏城实验室通信光电子研究所</x:v>
+      </x:c>
+      <x:c r="E34" s="6" t="str"/>
+      <x:c r="F34" s="6" t="str"/>
+      <x:c r="G34" s="6" t="str"/>
+      <x:c r="H34" s="6" t="str"/>
+      <x:c r="I34" s="6" t="str"/>
+      <x:c r="J34" s="6" t="str"/>
+      <x:c r="K34" s="6" t="str"/>
+      <x:c r="L34" s="6" t="str"/>
+      <x:c r="M34" s="7" t="str"/>
+      <x:c r="N34" s="6" t="str"/>
+      <x:c r="O34" s="6" t="str">
+        <x:v>2026-08-20浙大招聘简介明确历史岗位，未披露起讫。</x:v>
+      </x:c>
+      <x:c r="P34" s="6" t="str"/>
+      <x:c r="Q34" s="6" t="str">
+        <x:v>https://ehr.zju.edu.cn/vuejs/recruitment/position-detail.htm?id=N1873735234002879109</x:v>
+      </x:c>
+      <x:c r="R34" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S34" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="64" customHeight="1">
+      <x:c r="A35" s="6" t="str">
+        <x:v>曹子峥</x:v>
+      </x:c>
+      <x:c r="B35" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C35" s="6" t="str">
+        <x:v>量测方向首席科学家</x:v>
+      </x:c>
+      <x:c r="D35" s="6" t="str">
+        <x:v>Eindhoven Hendrik Casimir Institute（依托埃因霍温理工大学）</x:v>
+      </x:c>
+      <x:c r="E35" s="6" t="str"/>
+      <x:c r="F35" s="6" t="str"/>
+      <x:c r="G35" s="6" t="str"/>
+      <x:c r="H35" s="6" t="str"/>
+      <x:c r="I35" s="6" t="str"/>
+      <x:c r="J35" s="6" t="str"/>
+      <x:c r="K35" s="6" t="str"/>
+      <x:c r="L35" s="6" t="str"/>
+      <x:c r="M35" s="7" t="str"/>
+      <x:c r="N35" s="6" t="str"/>
+      <x:c r="O35" s="6" t="str">
+        <x:v>浙大2026招聘简介称该职务，未给起讫或全兼职性质，不据此推博士授位校。</x:v>
+      </x:c>
+      <x:c r="P35" s="6" t="str"/>
+      <x:c r="Q35" s="6" t="str">
+        <x:v>https://ehr.zju.edu.cn/vuejs/recruitment/position-detail.htm?id=N1873735234002879109</x:v>
+      </x:c>
+      <x:c r="R35" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S35" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="64" customHeight="1">
+      <x:c r="A36" s="6" t="str">
+        <x:v>韩雁</x:v>
+      </x:c>
+      <x:c r="B36" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C36" s="6" t="str"/>
+      <x:c r="D36" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+      <x:c r="E36" s="6" t="str"/>
+      <x:c r="F36" s="6" t="str">
+        <x:v>1982</x:v>
+      </x:c>
+      <x:c r="G36" s="6" t="str">
+        <x:v>半导体器件</x:v>
+      </x:c>
+      <x:c r="H36" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I36" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J36" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K36" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L36" s="6" t="str"/>
+      <x:c r="M36" s="7" t="str"/>
+      <x:c r="N36" s="6" t="str"/>
+      <x:c r="O36" s="6" t="str">
+        <x:v>原文明言1982毕业，但未写本科/学士；保持阶段及授位未知，不据年份顺序归类本科。</x:v>
+      </x:c>
+      <x:c r="P36" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q36" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/2025/0115/c81879a3012574/page.htm</x:v>
+      </x:c>
+      <x:c r="R36" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S36" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="64" customHeight="1">
+      <x:c r="A37" s="6" t="str">
+        <x:v>韩雁</x:v>
+      </x:c>
+      <x:c r="B37" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C37" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D37" s="6" t="str"/>
+      <x:c r="E37" s="6" t="str"/>
+      <x:c r="F37" s="6" t="str">
+        <x:v>1990</x:v>
+      </x:c>
+      <x:c r="G37" s="6" t="str"/>
+      <x:c r="H37" s="6" t="str"/>
+      <x:c r="I37" s="6" t="str"/>
+      <x:c r="J37" s="6" t="str"/>
+      <x:c r="K37" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L37" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M37" s="7" t="str"/>
+      <x:c r="N37" s="6" t="str"/>
+      <x:c r="O37" s="6" t="str">
+        <x:v>原文明言获学位，但未明确本阶段授位学校；不把上一句1982浙大毕业自动延伸到后两阶段。</x:v>
+      </x:c>
+      <x:c r="P37" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q37" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/2025/0115/c81879a3012574/page.htm</x:v>
+      </x:c>
+      <x:c r="R37" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S37" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="64" customHeight="1">
+      <x:c r="A38" s="6" t="str">
+        <x:v>韩雁</x:v>
+      </x:c>
+      <x:c r="B38" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C38" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D38" s="6" t="str"/>
+      <x:c r="E38" s="6" t="str"/>
+      <x:c r="F38" s="6" t="str">
+        <x:v>1995</x:v>
+      </x:c>
+      <x:c r="G38" s="6" t="str"/>
+      <x:c r="H38" s="6" t="str"/>
+      <x:c r="I38" s="6" t="str"/>
+      <x:c r="J38" s="6" t="str"/>
+      <x:c r="K38" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L38" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M38" s="7" t="str"/>
+      <x:c r="N38" s="6" t="str"/>
+      <x:c r="O38" s="6" t="str">
+        <x:v>原文明言获学位，但未明确本阶段授位学校；不把上一句1982浙大毕业自动延伸到后两阶段。</x:v>
+      </x:c>
+      <x:c r="P38" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q38" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/2025/0115/c81879a3012574/page.htm</x:v>
+      </x:c>
+      <x:c r="R38" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S38" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="64" customHeight="1">
+      <x:c r="A39" s="6" t="str">
+        <x:v>韩雁</x:v>
+      </x:c>
+      <x:c r="B39" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C39" s="6" t="str">
+        <x:v>教授、博士生导师</x:v>
+      </x:c>
+      <x:c r="D39" s="6" t="str">
+        <x:v>浙江大学集成电路学院</x:v>
+      </x:c>
+      <x:c r="E39" s="6" t="str"/>
+      <x:c r="F39" s="6" t="str"/>
+      <x:c r="G39" s="6" t="str"/>
+      <x:c r="H39" s="6" t="str"/>
+      <x:c r="I39" s="6" t="str"/>
+      <x:c r="J39" s="6" t="str"/>
+      <x:c r="K39" s="6" t="str"/>
+      <x:c r="L39" s="6" t="str"/>
+      <x:c r="M39" s="7" t="str"/>
+      <x:c r="N39" s="6" t="str"/>
+      <x:c r="O39" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P39" s="6" t="str"/>
+      <x:c r="Q39" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/jcdlxjzzjsyjs/list2.htm</x:v>
+      </x:c>
+      <x:c r="R39" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S39" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="64" customHeight="1">
+      <x:c r="A40" s="6" t="str">
+        <x:v>韩雁</x:v>
+      </x:c>
+      <x:c r="B40" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C40" s="6" t="str">
+        <x:v>副教授（晋升记录）</x:v>
+      </x:c>
+      <x:c r="D40" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+      <x:c r="E40" s="6" t="str">
+        <x:v>1996</x:v>
+      </x:c>
+      <x:c r="F40" s="6" t="str">
+        <x:v>2002</x:v>
+      </x:c>
+      <x:c r="G40" s="6" t="str"/>
+      <x:c r="H40" s="6" t="str"/>
+      <x:c r="I40" s="6" t="str"/>
+      <x:c r="J40" s="6" t="str"/>
+      <x:c r="K40" s="6" t="str"/>
+      <x:c r="L40" s="6" t="str"/>
+      <x:c r="M40" s="7" t="str"/>
+      <x:c r="N40" s="6" t="str"/>
+      <x:c r="O40" s="6" t="str"/>
+      <x:c r="P40" s="6" t="str"/>
+      <x:c r="Q40" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/2025/0115/c81879a3012574/page.htm</x:v>
+      </x:c>
+      <x:c r="R40" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S40" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="64" customHeight="1">
+      <x:c r="A41" s="6" t="str">
+        <x:v>韩雁</x:v>
+      </x:c>
+      <x:c r="B41" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C41" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D41" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+      <x:c r="E41" s="6" t="str">
+        <x:v>2002</x:v>
+      </x:c>
+      <x:c r="F41" s="6" t="str"/>
+      <x:c r="G41" s="6" t="str"/>
+      <x:c r="H41" s="6" t="str"/>
+      <x:c r="I41" s="6" t="str"/>
+      <x:c r="J41" s="6" t="str"/>
+      <x:c r="K41" s="6" t="str"/>
+      <x:c r="L41" s="6" t="str"/>
+      <x:c r="M41" s="7" t="str"/>
+      <x:c r="N41" s="6" t="str"/>
+      <x:c r="O41" s="6" t="str"/>
+      <x:c r="P41" s="6" t="str"/>
+      <x:c r="Q41" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/2025/0115/c81879a3012574/page.htm</x:v>
+      </x:c>
+      <x:c r="R41" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S41" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="64" customHeight="1">
+      <x:c r="A42" s="6" t="str">
+        <x:v>张睿</x:v>
+      </x:c>
+      <x:c r="B42" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C42" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D42" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E42" s="6" t="str"/>
+      <x:c r="F42" s="6" t="str">
+        <x:v>2006</x:v>
+      </x:c>
+      <x:c r="G42" s="6" t="str">
+        <x:v>材料科学与工程</x:v>
+      </x:c>
+      <x:c r="H42" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I42" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J42" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K42" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L42" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M42" s="7" t="str"/>
+      <x:c r="N42" s="6" t="str"/>
+      <x:c r="O42" s="6" t="str">
+        <x:v>出版者Author Bio明确received，作者姓名、浙大微纳电子单位和职业通信标识与官方本人页相同。</x:v>
+      </x:c>
+      <x:c r="P42" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q42" s="6" t="str">
+        <x:v>https://www.jos.ac.cn/article/id/5fac63df-cd6c-47dc-94ea-fe4e93ea190c?viewType=HTML</x:v>
+      </x:c>
+      <x:c r="R42" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S42" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="64" customHeight="1">
+      <x:c r="A43" s="6" t="str">
+        <x:v>张睿</x:v>
+      </x:c>
+      <x:c r="B43" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C43" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D43" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E43" s="6" t="str"/>
+      <x:c r="F43" s="6" t="str">
+        <x:v>2009</x:v>
+      </x:c>
+      <x:c r="G43" s="6" t="str">
+        <x:v>材料科学与工程</x:v>
+      </x:c>
+      <x:c r="H43" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I43" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J43" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K43" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L43" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M43" s="7" t="str"/>
+      <x:c r="N43" s="6" t="str"/>
+      <x:c r="O43" s="6" t="str">
+        <x:v>出版者Author Bio明确received，作者姓名、浙大微纳电子单位和职业通信标识与官方本人页相同。</x:v>
+      </x:c>
+      <x:c r="P43" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q43" s="6" t="str">
+        <x:v>https://www.jos.ac.cn/article/id/5fac63df-cd6c-47dc-94ea-fe4e93ea190c?viewType=HTML</x:v>
+      </x:c>
+      <x:c r="R43" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S43" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="64" customHeight="1">
+      <x:c r="A44" s="6" t="str">
+        <x:v>张睿</x:v>
+      </x:c>
+      <x:c r="B44" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C44" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D44" s="6" t="str">
+        <x:v>东京大学</x:v>
+      </x:c>
+      <x:c r="E44" s="6" t="str"/>
+      <x:c r="F44" s="6" t="str">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="G44" s="6" t="str">
+        <x:v>电气工程</x:v>
+      </x:c>
+      <x:c r="H44" s="6" t="str">
+        <x:v>日本</x:v>
+      </x:c>
+      <x:c r="I44" s="6" t="str">
+        <x:v>日本</x:v>
+      </x:c>
+      <x:c r="J44" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K44" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L44" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M44" s="7" t="str"/>
+      <x:c r="N44" s="6" t="str"/>
+      <x:c r="O44" s="6" t="str">
+        <x:v>出版者Author Bio明确received，作者姓名、浙大微纳电子单位和职业通信标识与官方本人页相同。</x:v>
+      </x:c>
+      <x:c r="P44" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q44" s="6" t="str">
+        <x:v>https://www.jos.ac.cn/article/id/5fac63df-cd6c-47dc-94ea-fe4e93ea190c?viewType=HTML</x:v>
+      </x:c>
+      <x:c r="R44" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S44" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="64" customHeight="1">
+      <x:c r="A45" s="6" t="str">
+        <x:v>张睿</x:v>
+      </x:c>
+      <x:c r="B45" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C45" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D45" s="6" t="str">
+        <x:v>浙江大学集成电路学院</x:v>
+      </x:c>
+      <x:c r="E45" s="6" t="str"/>
+      <x:c r="F45" s="6" t="str"/>
+      <x:c r="G45" s="6" t="str"/>
+      <x:c r="H45" s="6" t="str"/>
+      <x:c r="I45" s="6" t="str"/>
+      <x:c r="J45" s="6" t="str"/>
+      <x:c r="K45" s="6" t="str"/>
+      <x:c r="L45" s="6" t="str"/>
+      <x:c r="M45" s="7" t="str"/>
+      <x:c r="N45" s="6" t="str"/>
+      <x:c r="O45" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P45" s="6" t="str"/>
+      <x:c r="Q45" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/jcdlxjzzjsyjs/list2.htm</x:v>
+      </x:c>
+      <x:c r="R45" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S45" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="64" customHeight="1">
+      <x:c r="A46" s="6" t="str">
+        <x:v>张睿</x:v>
+      </x:c>
+      <x:c r="B46" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C46" s="6" t="str">
+        <x:v>副教授（2021年论文简介时点）</x:v>
+      </x:c>
+      <x:c r="D46" s="6" t="str">
+        <x:v>浙江大学微纳电子研究所</x:v>
+      </x:c>
+      <x:c r="E46" s="6" t="str"/>
+      <x:c r="F46" s="6" t="str"/>
+      <x:c r="G46" s="6" t="str"/>
+      <x:c r="H46" s="6" t="str"/>
+      <x:c r="I46" s="6" t="str"/>
+      <x:c r="J46" s="6" t="str"/>
+      <x:c r="K46" s="6" t="str"/>
+      <x:c r="L46" s="6" t="str"/>
+      <x:c r="M46" s="7" t="str"/>
+      <x:c r="N46" s="6" t="str"/>
+      <x:c r="O46" s="6" t="str"/>
+      <x:c r="P46" s="6" t="str"/>
+      <x:c r="Q46" s="6" t="str">
+        <x:v>https://www.jos.ac.cn/article/id/5fac63df-cd6c-47dc-94ea-fe4e93ea190c?viewType=HTML</x:v>
+      </x:c>
+      <x:c r="R46" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S46" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="64" customHeight="1">
+      <x:c r="A47" s="6" t="str">
+        <x:v>程然</x:v>
+      </x:c>
+      <x:c r="B47" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C47" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D47" s="6" t="str">
+        <x:v>新加坡国立大学</x:v>
+      </x:c>
+      <x:c r="E47" s="6" t="str"/>
+      <x:c r="F47" s="6" t="str">
+        <x:v>2009</x:v>
+      </x:c>
+      <x:c r="G47" s="6" t="str">
+        <x:v>电气工程</x:v>
+      </x:c>
+      <x:c r="H47" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="I47" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="J47" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K47" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L47" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M47" s="7" t="str"/>
+      <x:c r="N47" s="6" t="str"/>
+      <x:c r="O47" s="6" t="str">
+        <x:v>正式期刊Author Bio明确NUS于2009/2014获B.Eng./Ph.D.；先前西湖官方索引保留为辅助源，已用出版者直接正文完成授位核实。</x:v>
+      </x:c>
+      <x:c r="P47" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q47" s="6" t="str">
+        <x:v>https://www.jos.ac.cn/article/id/5fac63df-cd6c-47dc-94ea-fe4e93ea190c?viewType=HTML</x:v>
+      </x:c>
+      <x:c r="R47" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S47" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="64" customHeight="1">
+      <x:c r="A48" s="6" t="str">
+        <x:v>程然</x:v>
+      </x:c>
+      <x:c r="B48" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C48" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D48" s="6" t="str">
+        <x:v>新加坡国立大学</x:v>
+      </x:c>
+      <x:c r="E48" s="6" t="str"/>
+      <x:c r="F48" s="6" t="str">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="G48" s="6" t="str">
+        <x:v>电气工程</x:v>
+      </x:c>
+      <x:c r="H48" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="I48" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="J48" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K48" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L48" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M48" s="7" t="str"/>
+      <x:c r="N48" s="6" t="str"/>
+      <x:c r="O48" s="6" t="str">
+        <x:v>正式期刊Author Bio明确NUS于2009/2014获B.Eng./Ph.D.；先前西湖官方索引保留为辅助源，已用出版者直接正文完成授位核实。</x:v>
+      </x:c>
+      <x:c r="P48" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q48" s="6" t="str">
+        <x:v>https://www.jos.ac.cn/article/id/5fac63df-cd6c-47dc-94ea-fe4e93ea190c?viewType=HTML</x:v>
+      </x:c>
+      <x:c r="R48" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S48" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="64" customHeight="1">
+      <x:c r="A49" s="6" t="str">
+        <x:v>程然</x:v>
+      </x:c>
+      <x:c r="B49" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C49" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D49" s="6" t="str">
+        <x:v>浙江大学集成电路学院</x:v>
+      </x:c>
+      <x:c r="E49" s="6" t="str"/>
+      <x:c r="F49" s="6" t="str"/>
+      <x:c r="G49" s="6" t="str"/>
+      <x:c r="H49" s="6" t="str"/>
+      <x:c r="I49" s="6" t="str"/>
+      <x:c r="J49" s="6" t="str"/>
+      <x:c r="K49" s="6" t="str"/>
+      <x:c r="L49" s="6" t="str"/>
+      <x:c r="M49" s="7" t="str"/>
+      <x:c r="N49" s="6" t="str"/>
+      <x:c r="O49" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P49" s="6" t="str"/>
+      <x:c r="Q49" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/jcdlxjzzjsyjs/</x:v>
+      </x:c>
+      <x:c r="R49" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S49" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="64" customHeight="1">
+      <x:c r="A50" s="6" t="str">
+        <x:v>程然</x:v>
+      </x:c>
+      <x:c r="B50" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C50" s="6" t="str">
+        <x:v>加入任教</x:v>
+      </x:c>
+      <x:c r="D50" s="6" t="str">
+        <x:v>浙江大学微电子学院</x:v>
+      </x:c>
+      <x:c r="E50" s="6" t="str">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="F50" s="6" t="str"/>
+      <x:c r="G50" s="6" t="str"/>
+      <x:c r="H50" s="6" t="str"/>
+      <x:c r="I50" s="6" t="str"/>
+      <x:c r="J50" s="6" t="str"/>
+      <x:c r="K50" s="6" t="str"/>
+      <x:c r="L50" s="6" t="str"/>
+      <x:c r="M50" s="7" t="str"/>
+      <x:c r="N50" s="6" t="str"/>
+      <x:c r="O50" s="6" t="str">
+        <x:v>出版者简介原文late 2014，具体月份未知；不推同年已为副教授。</x:v>
+      </x:c>
+      <x:c r="P50" s="6" t="str"/>
+      <x:c r="Q50" s="6" t="str">
+        <x:v>https://www.jos.ac.cn/article/id/5fac63df-cd6c-47dc-94ea-fe4e93ea190c?viewType=HTML</x:v>
+      </x:c>
+      <x:c r="R50" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S50" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78a2ed679a17444e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d6fbc04558f4f4e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1314,8 +3039,159 @@
         <x:v>所属学校</x:v>
       </x:c>
     </x:row>
+    <x:row r="2" ht="64" customHeight="1">
+      <x:c r="A2" s="6" t="str">
+        <x:v>卓成</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>Noise-Aware DVFS for Efficient Transitions on Battery-Powered IoT Devices</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str"/>
+      <x:c r="E2" s="6" t="str">
+        <x:v>https://pi.zju.edu.cn/2022/0711/c68814a2603352/page.psp</x:v>
+      </x:c>
+      <x:c r="F2" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G2" s="6" t="str">
+        <x:v>https://pi.zju.edu.cn/2022/0711/c68814a2603352/page.psp</x:v>
+      </x:c>
+      <x:c r="H2" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/chengzhuo</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J2" s="6" t="str">
+        <x:v>工程师学院本人项目制导师栏目精选，未逐篇出版者链接。</x:v>
+      </x:c>
+      <x:c r="K2" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="L2" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="64" customHeight="1">
+      <x:c r="A3" s="6" t="str">
+        <x:v>卓成</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="str">
+        <x:v>Energy-Efficient Real-Time UAV Object Detection on Embedded Platforms</x:v>
+      </x:c>
+      <x:c r="C3" s="6" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="str"/>
+      <x:c r="E3" s="6" t="str">
+        <x:v>https://pi.zju.edu.cn/2022/0711/c68814a2603352/page.psp</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="str">
+        <x:v>https://pi.zju.edu.cn/2022/0711/c68814a2603352/page.psp</x:v>
+      </x:c>
+      <x:c r="H3" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/chengzhuo</x:v>
+      </x:c>
+      <x:c r="I3" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J3" s="6" t="str">
+        <x:v>工程师学院本人项目制导师栏目精选，未逐篇出版者链接。</x:v>
+      </x:c>
+      <x:c r="K3" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="L3" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="64" customHeight="1">
+      <x:c r="A4" s="6" t="str">
+        <x:v>张睿</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="str">
+        <x:v>Mobility enhancement techniques for Ge and GeSn MOSFETs</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="D4" s="6" t="str">
+        <x:v>10.1088/1674-4926/42/2/023101</x:v>
+      </x:c>
+      <x:c r="E4" s="6" t="str">
+        <x:v>https://www.jos.ac.cn/article/id/5fac63df-cd6c-47dc-94ea-fe4e93ea190c?viewType=HTML</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="str">
+        <x:v>https://www.jos.ac.cn/article/id/5fac63df-cd6c-47dc-94ea-fe4e93ea190c?viewType=HTML</x:v>
+      </x:c>
+      <x:c r="H4" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/0012183</x:v>
+      </x:c>
+      <x:c r="I4" s="6" t="str">
+        <x:v>article_metadata_verified</x:v>
+      </x:c>
+      <x:c r="J4" s="6" t="str">
+        <x:v>正式出版者正文作者简介同时提供教育证据；仅精选一篇，不从共同作者推导师。</x:v>
+      </x:c>
+      <x:c r="K4" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="L4" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="64" customHeight="1">
+      <x:c r="A5" s="6" t="str">
+        <x:v>程然</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="str">
+        <x:v>Mobility enhancement techniques for Ge and GeSn MOSFETs</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="str">
+        <x:v>10.1088/1674-4926/42/2/023101</x:v>
+      </x:c>
+      <x:c r="E5" s="6" t="str">
+        <x:v>https://www.jos.ac.cn/article/id/5fac63df-cd6c-47dc-94ea-fe4e93ea190c?viewType=HTML</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G5" s="6" t="str">
+        <x:v>https://www.jos.ac.cn/article/id/5fac63df-cd6c-47dc-94ea-fe4e93ea190c?viewType=HTML</x:v>
+      </x:c>
+      <x:c r="H5" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/chengran</x:v>
+      </x:c>
+      <x:c r="I5" s="6" t="str">
+        <x:v>article_metadata_verified</x:v>
+      </x:c>
+      <x:c r="J5" s="6" t="str">
+        <x:v>正式出版者全文作者简介；第一作者Ran Cheng的NUS/浙江大学半导体专业身份与此前官方讲座一致，排除香港理工AI同名人。</x:v>
+      </x:c>
+      <x:c r="K5" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="L5" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e316a248ab24e06"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
@@ -1564,31 +3440,652 @@
     </x:row>
     <x:row r="11" ht="64" customHeight="1">
       <x:c r="A11" s="6" t="str">
+        <x:v>程志渊</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>chengzhiyuan-source-1</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/jcdlxjzzjsyjs/</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="str">
+        <x:v>official_public_body_read</x:v>
+      </x:c>
+      <x:c r="E11" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F11" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G11" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="64" customHeight="1">
+      <x:c r="A12" s="6" t="str">
+        <x:v>程志渊</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
+        <x:v>chengzhiyuan-source-2</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str">
+        <x:v>https://www.kczg.org.cn/xuezhe/details?id=403894</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F12" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G12" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="64" customHeight="1">
+      <x:c r="A13" s="6" t="str">
+        <x:v>程志渊</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>chengzhiyuan-source-3</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="str">
+        <x:v>https://www.tsinghua.org.cn/info/1951/18473.htm</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F13" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G13" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="64" customHeight="1">
+      <x:c r="A14" s="6" t="str">
+        <x:v>程志渊</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="str">
+        <x:v>chengzhiyuan-source-4</x:v>
+      </x:c>
+      <x:c r="C14" s="6" t="str">
+        <x:v>https://hr.zju.edu.cn/postdoctor/2022/0427/c29115a2524719/page.htm</x:v>
+      </x:c>
+      <x:c r="D14" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F14" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G14" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="64" customHeight="1">
+      <x:c r="A15" s="6" t="str">
+        <x:v>卓成</x:v>
+      </x:c>
+      <x:c r="B15" s="6" t="str">
+        <x:v>zhuocheng-source-1</x:v>
+      </x:c>
+      <x:c r="C15" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/jcdlxjzzjsyjs/</x:v>
+      </x:c>
+      <x:c r="D15" s="6" t="str">
+        <x:v>official_public_body_read</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F15" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G15" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="64" customHeight="1">
+      <x:c r="A16" s="6" t="str">
+        <x:v>卓成</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="str">
+        <x:v>zhuocheng-source-2</x:v>
+      </x:c>
+      <x:c r="C16" s="6" t="str">
+        <x:v>https://www.szics.net/guests/124/</x:v>
+      </x:c>
+      <x:c r="D16" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F16" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G16" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="64" customHeight="1">
+      <x:c r="A17" s="6" t="str">
+        <x:v>卓成</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="str">
+        <x:v>zhuocheng-source-3</x:v>
+      </x:c>
+      <x:c r="C17" s="6" t="str">
+        <x:v>https://deepblue.lib.umich.edu/bitstream/handle/2027.42/84481/czhuo_1.pdf?isAllowed=y&amp;sequence=1</x:v>
+      </x:c>
+      <x:c r="D17" s="6" t="str">
+        <x:v>official_dissertation_search_index_only_direct_429</x:v>
+      </x:c>
+      <x:c r="E17" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F17" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G17" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="64" customHeight="1">
+      <x:c r="A18" s="6" t="str">
+        <x:v>卓成</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="str">
+        <x:v>zhuocheng-source-4</x:v>
+      </x:c>
+      <x:c r="C18" s="6" t="str">
+        <x:v>https://xxgk.hfut.edu.cn/2022/0904/c4772a282515/page.htm</x:v>
+      </x:c>
+      <x:c r="D18" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F18" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G18" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="64" customHeight="1">
+      <x:c r="A19" s="6" t="str">
+        <x:v>卓成</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>zhuocheng-source-5</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/2026/0507/c53931a3159480/page.psp</x:v>
+      </x:c>
+      <x:c r="D19" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E19" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F19" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G19" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="64" customHeight="1">
+      <x:c r="A20" s="6" t="str">
+        <x:v>卓成</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>zhuocheng-source-6</x:v>
+      </x:c>
+      <x:c r="C20" s="6" t="str">
+        <x:v>https://pi.zju.edu.cn/2022/0711/c68814a2603352/page.psp</x:v>
+      </x:c>
+      <x:c r="D20" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E20" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F20" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G20" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="64" customHeight="1">
+      <x:c r="A21" s="6" t="str">
+        <x:v>曹子峥</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="str">
+        <x:v>caozizheng-source-1</x:v>
+      </x:c>
+      <x:c r="C21" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/jcdlxjzzjsyjs/</x:v>
+      </x:c>
+      <x:c r="D21" s="6" t="str">
+        <x:v>official_public_body_read</x:v>
+      </x:c>
+      <x:c r="E21" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F21" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G21" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="64" customHeight="1">
+      <x:c r="A22" s="6" t="str">
+        <x:v>曹子峥</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="str">
+        <x:v>caozizheng-source-2</x:v>
+      </x:c>
+      <x:c r="C22" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/zzcao</x:v>
+      </x:c>
+      <x:c r="D22" s="6" t="str">
+        <x:v>official_profile_header_web_read_local_fetch_403_stopped</x:v>
+      </x:c>
+      <x:c r="E22" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F22" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G22" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="64" customHeight="1">
+      <x:c r="A23" s="6" t="str">
+        <x:v>曹子峥</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="str">
+        <x:v>caozizheng-source-3</x:v>
+      </x:c>
+      <x:c r="C23" s="6" t="str">
+        <x:v>https://ehr.zju.edu.cn/vuejs/recruitment/position-detail.htm?id=N1873735234002879109</x:v>
+      </x:c>
+      <x:c r="D23" s="6" t="str">
+        <x:v>official_public_recruitment_page_rendered_data_read</x:v>
+      </x:c>
+      <x:c r="E23" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F23" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G23" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="64" customHeight="1">
+      <x:c r="A24" s="6" t="str">
+        <x:v>韩雁</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="str">
+        <x:v>hanyan-source-1</x:v>
+      </x:c>
+      <x:c r="C24" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/jcdlxjzzjsyjs/list2.htm</x:v>
+      </x:c>
+      <x:c r="D24" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E24" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F24" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G24" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="64" customHeight="1">
+      <x:c r="A25" s="6" t="str">
+        <x:v>韩雁</x:v>
+      </x:c>
+      <x:c r="B25" s="6" t="str">
+        <x:v>hanyan-source-2</x:v>
+      </x:c>
+      <x:c r="C25" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/2025/0115/c81879a3012574/page.htm</x:v>
+      </x:c>
+      <x:c r="D25" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E25" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F25" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G25" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="64" customHeight="1">
+      <x:c r="A26" s="6" t="str">
+        <x:v>张睿</x:v>
+      </x:c>
+      <x:c r="B26" s="6" t="str">
+        <x:v>zhangrui-source-1</x:v>
+      </x:c>
+      <x:c r="C26" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/jcdlxjzzjsyjs/list2.htm</x:v>
+      </x:c>
+      <x:c r="D26" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E26" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F26" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G26" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="64" customHeight="1">
+      <x:c r="A27" s="6" t="str">
+        <x:v>张睿</x:v>
+      </x:c>
+      <x:c r="B27" s="6" t="str">
+        <x:v>zhangrui-source-2</x:v>
+      </x:c>
+      <x:c r="C27" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/0012183</x:v>
+      </x:c>
+      <x:c r="D27" s="6" t="str">
+        <x:v>official_profile_header_web_read_local_403_stopped</x:v>
+      </x:c>
+      <x:c r="E27" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F27" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G27" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="64" customHeight="1">
+      <x:c r="A28" s="6" t="str">
+        <x:v>张睿</x:v>
+      </x:c>
+      <x:c r="B28" s="6" t="str">
+        <x:v>zhangrui-source-3</x:v>
+      </x:c>
+      <x:c r="C28" s="6" t="str">
+        <x:v>https://www.jos.ac.cn/article/id/5fac63df-cd6c-47dc-94ea-fe4e93ea190c?viewType=HTML</x:v>
+      </x:c>
+      <x:c r="D28" s="6" t="str">
+        <x:v>publisher_article_author_biography_direct_read</x:v>
+      </x:c>
+      <x:c r="E28" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F28" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G28" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="64" customHeight="1">
+      <x:c r="A29" s="6" t="str">
+        <x:v>程然</x:v>
+      </x:c>
+      <x:c r="B29" s="6" t="str">
+        <x:v>chengran-source-1</x:v>
+      </x:c>
+      <x:c r="C29" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/jcdlxjzzjsyjs/</x:v>
+      </x:c>
+      <x:c r="D29" s="6" t="str">
+        <x:v>official_public_body_read</x:v>
+      </x:c>
+      <x:c r="E29" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F29" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G29" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="64" customHeight="1">
+      <x:c r="A30" s="6" t="str">
+        <x:v>程然</x:v>
+      </x:c>
+      <x:c r="B30" s="6" t="str">
+        <x:v>chengran-source-2</x:v>
+      </x:c>
+      <x:c r="C30" s="6" t="str">
+        <x:v>https://engineering.westlake.edu.cn/NewsEvents/RecentEvents/202412/t20241230_51420.shtml</x:v>
+      </x:c>
+      <x:c r="D30" s="6" t="str">
+        <x:v>official_institution_search_index_full_biography_direct_page_unavailable</x:v>
+      </x:c>
+      <x:c r="E30" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F30" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G30" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="64" customHeight="1">
+      <x:c r="A31" s="6" t="str">
+        <x:v>程然</x:v>
+      </x:c>
+      <x:c r="B31" s="6" t="str">
+        <x:v>chengran-source-3</x:v>
+      </x:c>
+      <x:c r="C31" s="6" t="str">
+        <x:v>https://www.jos.ac.cn/article/id/5fac63df-cd6c-47dc-94ea-fe4e93ea190c?viewType=HTML</x:v>
+      </x:c>
+      <x:c r="D31" s="6" t="str">
+        <x:v>publisher_article_author_biography_direct_read</x:v>
+      </x:c>
+      <x:c r="E31" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F31" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G31" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="64" customHeight="1">
+      <x:c r="A32" s="6" t="str">
         <x:v>綦殿禹</x:v>
       </x:c>
-      <x:c r="B11" s="6" t="str">
+      <x:c r="B32" s="6" t="str">
         <x:v>institution-classification-2</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="C32" s="6" t="str">
         <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="D32" s="6" t="str">
         <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
       </x:c>
-      <x:c r="E11" s="7" t="d">
-        <x:v>2026-10-23T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="F11" s="6" t="str">
-        <x:v>zju</x:v>
-      </x:c>
-      <x:c r="G11" s="6" t="str">
+      <x:c r="E32" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F32" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G32" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="64" customHeight="1">
+      <x:c r="A33" s="6" t="str">
+        <x:v>程志渊</x:v>
+      </x:c>
+      <x:c r="B33" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C33" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D33" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E33" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F33" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G33" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="64" customHeight="1">
+      <x:c r="A34" s="6" t="str">
+        <x:v>程志渊</x:v>
+      </x:c>
+      <x:c r="B34" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C34" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D34" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E34" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F34" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G34" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="64" customHeight="1">
+      <x:c r="A35" s="6" t="str">
+        <x:v>卓成</x:v>
+      </x:c>
+      <x:c r="B35" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C35" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D35" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E35" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F35" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G35" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="64" customHeight="1">
+      <x:c r="A36" s="6" t="str">
+        <x:v>韩雁</x:v>
+      </x:c>
+      <x:c r="B36" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C36" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D36" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E36" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F36" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G36" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="64" customHeight="1">
+      <x:c r="A37" s="6" t="str">
+        <x:v>张睿</x:v>
+      </x:c>
+      <x:c r="B37" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C37" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D37" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E37" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F37" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G37" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="64" customHeight="1">
+      <x:c r="A38" s="6" t="str">
+        <x:v>张睿</x:v>
+      </x:c>
+      <x:c r="B38" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C38" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D38" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E38" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F38" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G38" s="6" t="str">
         <x:v>浙江大学</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b0e2db9bf644f8e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14d9f4f5885048ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/zju-ic-manufacturing.xlsx
+++ b/site/exports/zju-ic-manufacturing.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R2ee17c10119f4d8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R098d587d39d54d39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Ree2f66bd3855443e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Rb4134934d59142e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R0f1e9728d7734aad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R067c829f947041b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Rbaed432908ef4fca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rd6bbf00e635a4b25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Rd248767c691a4da9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R221e5ce5e78b4e27"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T10_0" displayName="T10_0" ref="A1:K10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T10_0" displayName="T10_0" ref="A1:K14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T10_1" displayName="T10_1" ref="A1:S50" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T10_1" displayName="T10_1" ref="A1:S71" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -185,7 +185,27 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T10_3" displayName="T10_3" ref="A1:L5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T10_2" displayName="T10_2" ref="A1:L8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="12">
+    <x:tableColumn id="1" name="姓名"/>
+    <x:tableColumn id="2" name="导师姓名"/>
+    <x:tableColumn id="3" name="关系类型"/>
+    <x:tableColumn id="4" name="阶段"/>
+    <x:tableColumn id="5" name="简介"/>
+    <x:tableColumn id="6" name="在职状态"/>
+    <x:tableColumn id="7" name="状态说明"/>
+    <x:tableColumn id="8" name="已核在职主页"/>
+    <x:tableColumn id="9" name="关系来源"/>
+    <x:tableColumn id="10" name="任职来源"/>
+    <x:tableColumn id="11" name="所属学校ID"/>
+    <x:tableColumn id="12" name="所属学校"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T10_3" displayName="T10_3" ref="A1:L7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
@@ -204,8 +224,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T10_4" displayName="T10_4" ref="A1:G38" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T10_4" displayName="T10_4" ref="A1:G63" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -759,10 +779,142 @@
         <x:v>浙江大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="11" ht="64" customHeight="1">
+      <x:c r="A11" s="6" t="str">
+        <x:v>张运炎</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="str">
+        <x:v>集成电路学院·先进集成电路制造技术研究所</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/123321</x:v>
+      </x:c>
+      <x:c r="E11" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F11" s="6" t="str">
+        <x:v>本人主页403，停止读取该页；本科及导师未确证。；博士年份中科院2015/会议2012冲突，不取无争议年份；UCL论文库检索题录2015仅辅助，未宣称正文已读。</x:v>
+      </x:c>
+      <x:c r="G11" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H11" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I11" s="6" t="str"/>
+      <x:c r="J11" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="K11" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="64" customHeight="1">
+      <x:c r="A12" s="6" t="str">
+        <x:v>孙奇</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str">
+        <x:v>集成电路学院·先进集成电路制造技术研究所</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/0023146</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F12" s="6" t="str">
+        <x:v>浙大标准个人页403停止；本人独立职业网站身份交叉吻合后使用，不由此声称标准页可达。；未取得本科年月/专业、博士起始月及本科导师；精选论文暂未逐篇核。</x:v>
+      </x:c>
+      <x:c r="G12" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H12" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I12" s="6" t="str"/>
+      <x:c r="J12" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="K12" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="64" customHeight="1">
+      <x:c r="A13" s="6" t="str">
+        <x:v>李骏康</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="str">
+        <x:v>集成电路学院·先进集成电路制造技术研究所</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/JunkangLi</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F13" s="6" t="str">
+        <x:v>本人博士头部可核，但本科/硕士、博士授位机构年月尚不足；不把2020在读新闻当毕业证据。；普渡访问导师未核。</x:v>
+      </x:c>
+      <x:c r="G13" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H13" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I13" s="6" t="str"/>
+      <x:c r="J13" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="K13" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="64" customHeight="1">
+      <x:c r="A14" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C14" s="6" t="str">
+        <x:v>集成电路学院·先进集成电路制造技术研究所</x:v>
+      </x:c>
+      <x:c r="D14" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/zyan2</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F14" s="6" t="str">
+        <x:v>博士完成年月2023.12/2024.05及博士后开始2023.12/2024.02不同来源冲突，保留未知不强定。；2024毕业典礼手册还列MS，未核该硕士完整事件/授位日期，列补证事项不猜顺序。；CV与ND本科专业标签不同；不同同名人脸识别作者不合并。</x:v>
+      </x:c>
+      <x:c r="G14" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H14" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I14" s="6" t="str"/>
+      <x:c r="J14" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="K14" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R869e4aa55d05416f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re039f7ebbdd34140"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2914,10 +3066,931 @@
         <x:v>浙江大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="51" ht="64" customHeight="1">
+      <x:c r="A51" s="6" t="str">
+        <x:v>张运炎</x:v>
+      </x:c>
+      <x:c r="B51" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C51" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D51" s="6" t="str">
+        <x:v>华南师范大学</x:v>
+      </x:c>
+      <x:c r="E51" s="6" t="str"/>
+      <x:c r="F51" s="6" t="str">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="G51" s="6" t="str"/>
+      <x:c r="H51" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I51" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J51" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K51" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L51" s="6" t="str"/>
+      <x:c r="M51" s="7" t="str"/>
+      <x:c r="N51" s="6" t="str"/>
+      <x:c r="O51" s="6" t="str">
+        <x:v>官方报告简介明确硕士毕业，未明说授予学位，暂保守null；专业仅研究氮化物LED，不能当学位专业。</x:v>
+      </x:c>
+      <x:c r="P51" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q51" s="6" t="str">
+        <x:v>https://optics.iphy.ac.cn/detail.php?id=29448</x:v>
+      </x:c>
+      <x:c r="R51" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S51" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="64" customHeight="1">
+      <x:c r="A52" s="6" t="str">
+        <x:v>张运炎</x:v>
+      </x:c>
+      <x:c r="B52" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C52" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D52" s="6" t="str">
+        <x:v>伦敦大学学院</x:v>
+      </x:c>
+      <x:c r="E52" s="6" t="str"/>
+      <x:c r="F52" s="6" t="str"/>
+      <x:c r="G52" s="6" t="str"/>
+      <x:c r="H52" s="6" t="str">
+        <x:v>英国</x:v>
+      </x:c>
+      <x:c r="I52" s="6" t="str">
+        <x:v>英国</x:v>
+      </x:c>
+      <x:c r="J52" s="6" t="str">
+        <x:v>欧洲</x:v>
+      </x:c>
+      <x:c r="K52" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L52" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M52" s="7" t="str"/>
+      <x:c r="N52" s="6" t="str"/>
+      <x:c r="O52" s="6" t="str">
+        <x:v>中科院简介明确2015获得；2018会议手册阅读器28页称2012，年份冲突，end留空，不取消已确证博士。</x:v>
+      </x:c>
+      <x:c r="P52" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q52" s="6" t="str">
+        <x:v>https://optics.iphy.ac.cn/detail.php?id=29448</x:v>
+      </x:c>
+      <x:c r="R52" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S52" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="64" customHeight="1">
+      <x:c r="A53" s="6" t="str">
+        <x:v>张运炎</x:v>
+      </x:c>
+      <x:c r="B53" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C53" s="6" t="str">
+        <x:v>百人计划研究员</x:v>
+      </x:c>
+      <x:c r="D53" s="6" t="str">
+        <x:v>浙江大学集成电路学院</x:v>
+      </x:c>
+      <x:c r="E53" s="6" t="str"/>
+      <x:c r="F53" s="6" t="str"/>
+      <x:c r="G53" s="6" t="str"/>
+      <x:c r="H53" s="6" t="str"/>
+      <x:c r="I53" s="6" t="str"/>
+      <x:c r="J53" s="6" t="str"/>
+      <x:c r="K53" s="6" t="str"/>
+      <x:c r="L53" s="6" t="str"/>
+      <x:c r="M53" s="7" t="str"/>
+      <x:c r="N53" s="6" t="str"/>
+      <x:c r="O53" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P53" s="6" t="str"/>
+      <x:c r="Q53" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/jcdlxjzzjsyjs/list2.htm</x:v>
+      </x:c>
+      <x:c r="R53" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S53" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="64" customHeight="1">
+      <x:c r="A54" s="6" t="str">
+        <x:v>张运炎</x:v>
+      </x:c>
+      <x:c r="B54" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C54" s="6" t="str">
+        <x:v>研究助理</x:v>
+      </x:c>
+      <x:c r="D54" s="6" t="str">
+        <x:v>香港科技大学</x:v>
+      </x:c>
+      <x:c r="E54" s="6" t="str">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="F54" s="6" t="str">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="G54" s="6" t="str"/>
+      <x:c r="H54" s="6" t="str"/>
+      <x:c r="I54" s="6" t="str"/>
+      <x:c r="J54" s="6" t="str"/>
+      <x:c r="K54" s="6" t="str"/>
+      <x:c r="L54" s="6" t="str"/>
+      <x:c r="M54" s="7" t="str"/>
+      <x:c r="N54" s="6" t="str"/>
+      <x:c r="O54" s="6" t="str"/>
+      <x:c r="P54" s="6" t="str"/>
+      <x:c r="Q54" s="6" t="str">
+        <x:v>https://optics.iphy.ac.cn/detail.php?id=29448</x:v>
+      </x:c>
+      <x:c r="R54" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S54" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="64" customHeight="1">
+      <x:c r="A55" s="6" t="str">
+        <x:v>张运炎</x:v>
+      </x:c>
+      <x:c r="B55" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C55" s="6" t="str">
+        <x:v>研究助理</x:v>
+      </x:c>
+      <x:c r="D55" s="6" t="str">
+        <x:v>伦敦大学学院</x:v>
+      </x:c>
+      <x:c r="E55" s="6" t="str">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="F55" s="6" t="str"/>
+      <x:c r="G55" s="6" t="str"/>
+      <x:c r="H55" s="6" t="str"/>
+      <x:c r="I55" s="6" t="str"/>
+      <x:c r="J55" s="6" t="str"/>
+      <x:c r="K55" s="6" t="str"/>
+      <x:c r="L55" s="6" t="str"/>
+      <x:c r="M55" s="7" t="str"/>
+      <x:c r="N55" s="6" t="str"/>
+      <x:c r="O55" s="6" t="str">
+        <x:v>截至2017年报道为当时现职，不表示今天仍任职；2018会议手册又称自2012，起年存在冲突。</x:v>
+      </x:c>
+      <x:c r="P55" s="6" t="str"/>
+      <x:c r="Q55" s="6" t="str">
+        <x:v>https://optics.iphy.ac.cn/detail.php?id=29448</x:v>
+      </x:c>
+      <x:c r="R55" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S55" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="64" customHeight="1">
+      <x:c r="A56" s="6" t="str">
+        <x:v>孙奇</x:v>
+      </x:c>
+      <x:c r="B56" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C56" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D56" s="6" t="str">
+        <x:v>西安电子科技大学</x:v>
+      </x:c>
+      <x:c r="E56" s="6" t="str"/>
+      <x:c r="F56" s="6" t="str"/>
+      <x:c r="G56" s="6" t="str"/>
+      <x:c r="H56" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I56" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J56" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K56" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L56" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M56" s="7" t="str"/>
+      <x:c r="N56" s="6" t="str"/>
+      <x:c r="O56" s="6" t="str">
+        <x:v>本人主页B.Eng.列示，年份/专业未披露。</x:v>
+      </x:c>
+      <x:c r="P56" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q56" s="6" t="str">
+        <x:v>https://qisunchn.top/index.html</x:v>
+      </x:c>
+      <x:c r="R56" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S56" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="64" customHeight="1">
+      <x:c r="A57" s="6" t="str">
+        <x:v>孙奇</x:v>
+      </x:c>
+      <x:c r="B57" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C57" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D57" s="6" t="str">
+        <x:v>香港中文大学</x:v>
+      </x:c>
+      <x:c r="E57" s="6" t="str"/>
+      <x:c r="F57" s="6" t="str">
+        <x:v>2022-07</x:v>
+      </x:c>
+      <x:c r="G57" s="6" t="str">
+        <x:v>计算机科学与工程</x:v>
+      </x:c>
+      <x:c r="H57" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I57" s="6" t="str">
+        <x:v>中国香港</x:v>
+      </x:c>
+      <x:c r="J57" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K57" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L57" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M57" s="7" t="str"/>
+      <x:c r="N57" s="6" t="str"/>
+      <x:c r="O57" s="6" t="str"/>
+      <x:c r="P57" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q57" s="6" t="str">
+        <x:v>https://qisunchn.top/index.html</x:v>
+      </x:c>
+      <x:c r="R57" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S57" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="64" customHeight="1">
+      <x:c r="A58" s="6" t="str">
+        <x:v>孙奇</x:v>
+      </x:c>
+      <x:c r="B58" s="6" t="str">
+        <x:v>postdoctoral_research</x:v>
+      </x:c>
+      <x:c r="C58" s="6" t="str"/>
+      <x:c r="D58" s="6" t="str">
+        <x:v>康奈尔大学</x:v>
+      </x:c>
+      <x:c r="E58" s="6" t="str">
+        <x:v>2022-09</x:v>
+      </x:c>
+      <x:c r="F58" s="6" t="str">
+        <x:v>2023-08</x:v>
+      </x:c>
+      <x:c r="G58" s="6" t="str"/>
+      <x:c r="H58" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="I58" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="J58" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K58" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L58" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M58" s="7" t="str"/>
+      <x:c r="N58" s="6" t="str"/>
+      <x:c r="O58" s="6" t="str"/>
+      <x:c r="P58" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q58" s="6" t="str">
+        <x:v>https://qisunchn.top/experience.html</x:v>
+      </x:c>
+      <x:c r="R58" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S58" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="64" customHeight="1">
+      <x:c r="A59" s="6" t="str">
+        <x:v>孙奇</x:v>
+      </x:c>
+      <x:c r="B59" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C59" s="6" t="str">
+        <x:v>百人计划研究员</x:v>
+      </x:c>
+      <x:c r="D59" s="6" t="str">
+        <x:v>浙江大学集成电路学院</x:v>
+      </x:c>
+      <x:c r="E59" s="6" t="str"/>
+      <x:c r="F59" s="6" t="str"/>
+      <x:c r="G59" s="6" t="str"/>
+      <x:c r="H59" s="6" t="str"/>
+      <x:c r="I59" s="6" t="str"/>
+      <x:c r="J59" s="6" t="str"/>
+      <x:c r="K59" s="6" t="str"/>
+      <x:c r="L59" s="6" t="str"/>
+      <x:c r="M59" s="7" t="str"/>
+      <x:c r="N59" s="6" t="str"/>
+      <x:c r="O59" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P59" s="6" t="str"/>
+      <x:c r="Q59" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/jcdlxjzzjsyjs/list2.htm</x:v>
+      </x:c>
+      <x:c r="R59" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S59" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="64" customHeight="1">
+      <x:c r="A60" s="6" t="str">
+        <x:v>孙奇</x:v>
+      </x:c>
+      <x:c r="B60" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C60" s="6" t="str">
+        <x:v>Post-doctoral Associate</x:v>
+      </x:c>
+      <x:c r="D60" s="6" t="str">
+        <x:v>康奈尔大学</x:v>
+      </x:c>
+      <x:c r="E60" s="6" t="str">
+        <x:v>2022-09</x:v>
+      </x:c>
+      <x:c r="F60" s="6" t="str">
+        <x:v>2023-08</x:v>
+      </x:c>
+      <x:c r="G60" s="6" t="str"/>
+      <x:c r="H60" s="6" t="str"/>
+      <x:c r="I60" s="6" t="str"/>
+      <x:c r="J60" s="6" t="str"/>
+      <x:c r="K60" s="6" t="str"/>
+      <x:c r="L60" s="6" t="str"/>
+      <x:c r="M60" s="7" t="str"/>
+      <x:c r="N60" s="6" t="str"/>
+      <x:c r="O60" s="6" t="str"/>
+      <x:c r="P60" s="6" t="str"/>
+      <x:c r="Q60" s="6" t="str">
+        <x:v>https://qisunchn.top/experience.html</x:v>
+      </x:c>
+      <x:c r="R60" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S60" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="64" customHeight="1">
+      <x:c r="A61" s="6" t="str">
+        <x:v>孙奇</x:v>
+      </x:c>
+      <x:c r="B61" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C61" s="6" t="str">
+        <x:v>Research Intern</x:v>
+      </x:c>
+      <x:c r="D61" s="6" t="str">
+        <x:v>SmartMore</x:v>
+      </x:c>
+      <x:c r="E61" s="6" t="str">
+        <x:v>2020-03</x:v>
+      </x:c>
+      <x:c r="F61" s="6" t="str">
+        <x:v>2022-06</x:v>
+      </x:c>
+      <x:c r="G61" s="6" t="str"/>
+      <x:c r="H61" s="6" t="str"/>
+      <x:c r="I61" s="6" t="str"/>
+      <x:c r="J61" s="6" t="str"/>
+      <x:c r="K61" s="6" t="str"/>
+      <x:c r="L61" s="6" t="str"/>
+      <x:c r="M61" s="7" t="str"/>
+      <x:c r="N61" s="6" t="str"/>
+      <x:c r="O61" s="6" t="str">
+        <x:v>香港实习岗位，非学位/访问学者。</x:v>
+      </x:c>
+      <x:c r="P61" s="6" t="str"/>
+      <x:c r="Q61" s="6" t="str">
+        <x:v>https://qisunchn.top/experience.html</x:v>
+      </x:c>
+      <x:c r="R61" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S61" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="64" customHeight="1">
+      <x:c r="A62" s="6" t="str">
+        <x:v>李骏康</x:v>
+      </x:c>
+      <x:c r="B62" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C62" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D62" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+      <x:c r="E62" s="6" t="str"/>
+      <x:c r="F62" s="6" t="str"/>
+      <x:c r="G62" s="6" t="str"/>
+      <x:c r="H62" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I62" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J62" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K62" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L62" s="6" t="str"/>
+      <x:c r="M62" s="7" t="str"/>
+      <x:c r="N62" s="6" t="str"/>
+      <x:c r="O62" s="6" t="str">
+        <x:v>2020学院新闻明确张睿的博士研究生；目前本人头部博士，但没有独立指明其博士授位机构/日期，本条仅保留浙大博士学习待授位核。</x:v>
+      </x:c>
+      <x:c r="P62" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q62" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/2020/1220/c53675a2235682/page.htm</x:v>
+      </x:c>
+      <x:c r="R62" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S62" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="64" customHeight="1">
+      <x:c r="A63" s="6" t="str">
+        <x:v>李骏康</x:v>
+      </x:c>
+      <x:c r="B63" s="6" t="str">
+        <x:v>visiting_scholar</x:v>
+      </x:c>
+      <x:c r="C63" s="6" t="str"/>
+      <x:c r="D63" s="6" t="str">
+        <x:v>普渡大学</x:v>
+      </x:c>
+      <x:c r="E63" s="6" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="F63" s="6" t="str">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="G63" s="6" t="str"/>
+      <x:c r="H63" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="I63" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="J63" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K63" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L63" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M63" s="7" t="str"/>
+      <x:c r="N63" s="6" t="str"/>
+      <x:c r="O63" s="6" t="str"/>
+      <x:c r="P63" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q63" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/2020/1220/c53675a2235682/page.htm</x:v>
+      </x:c>
+      <x:c r="R63" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S63" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="64" customHeight="1">
+      <x:c r="A64" s="6" t="str">
+        <x:v>李骏康</x:v>
+      </x:c>
+      <x:c r="B64" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C64" s="6" t="str">
+        <x:v>百人计划研究员</x:v>
+      </x:c>
+      <x:c r="D64" s="6" t="str">
+        <x:v>浙江大学集成电路学院</x:v>
+      </x:c>
+      <x:c r="E64" s="6" t="str"/>
+      <x:c r="F64" s="6" t="str"/>
+      <x:c r="G64" s="6" t="str"/>
+      <x:c r="H64" s="6" t="str"/>
+      <x:c r="I64" s="6" t="str"/>
+      <x:c r="J64" s="6" t="str"/>
+      <x:c r="K64" s="6" t="str"/>
+      <x:c r="L64" s="6" t="str"/>
+      <x:c r="M64" s="7" t="str"/>
+      <x:c r="N64" s="6" t="str"/>
+      <x:c r="O64" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P64" s="6" t="str"/>
+      <x:c r="Q64" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/jcdlxjzzjsyjs/list2.htm</x:v>
+      </x:c>
+      <x:c r="R64" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S64" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="64" customHeight="1">
+      <x:c r="A65" s="6" t="str">
+        <x:v>李骏康</x:v>
+      </x:c>
+      <x:c r="B65" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C65" s="6" t="str">
+        <x:v>访问学者</x:v>
+      </x:c>
+      <x:c r="D65" s="6" t="str">
+        <x:v>普渡大学</x:v>
+      </x:c>
+      <x:c r="E65" s="6" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="F65" s="6" t="str">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="G65" s="6" t="str"/>
+      <x:c r="H65" s="6" t="str"/>
+      <x:c r="I65" s="6" t="str"/>
+      <x:c r="J65" s="6" t="str"/>
+      <x:c r="K65" s="6" t="str"/>
+      <x:c r="L65" s="6" t="str"/>
+      <x:c r="M65" s="7" t="str"/>
+      <x:c r="N65" s="6" t="str"/>
+      <x:c r="O65" s="6" t="str"/>
+      <x:c r="P65" s="6" t="str"/>
+      <x:c r="Q65" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/2020/1220/c53675a2235682/page.htm</x:v>
+      </x:c>
+      <x:c r="R65" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S65" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="64" customHeight="1">
+      <x:c r="A66" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B66" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C66" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D66" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+      <x:c r="E66" s="6" t="str">
+        <x:v>2015-08</x:v>
+      </x:c>
+      <x:c r="F66" s="6" t="str">
+        <x:v>2019-06</x:v>
+      </x:c>
+      <x:c r="G66" s="6" t="str">
+        <x:v>Electronic Science and Technology</x:v>
+      </x:c>
+      <x:c r="H66" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I66" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J66" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K66" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L66" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M66" s="7" t="str"/>
+      <x:c r="N66" s="6" t="str"/>
+      <x:c r="O66" s="6" t="str">
+        <x:v>学位获授及2019来自ND本人页，起始月/结束月来自本人CV；CV专业Electronic Engineering与ND页专业名称不同保留。</x:v>
+      </x:c>
+      <x:c r="P66" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q66" s="6" t="str">
+        <x:v>https://sites.nd.edu/zheyu-yan/</x:v>
+      </x:c>
+      <x:c r="R66" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S66" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="64" customHeight="1">
+      <x:c r="A67" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B67" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C67" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D67" s="6" t="str">
+        <x:v>圣母大学</x:v>
+      </x:c>
+      <x:c r="E67" s="6" t="str">
+        <x:v>2019-08</x:v>
+      </x:c>
+      <x:c r="F67" s="6" t="str"/>
+      <x:c r="G67" s="6" t="str">
+        <x:v>Computer Science and Engineering</x:v>
+      </x:c>
+      <x:c r="H67" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="I67" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="J67" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K67" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L67" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M67" s="7" t="str"/>
+      <x:c r="N67" s="6" t="str"/>
+      <x:c r="O67" s="6" t="str">
+        <x:v>本人ND页称2024，CV结束2024.05；导师Hu2024CV称2023.12，毕业/授位时间冲突，end留空，仍明确已获博士。</x:v>
+      </x:c>
+      <x:c r="P67" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q67" s="6" t="str">
+        <x:v>https://sites.nd.edu/zheyu-yan/</x:v>
+      </x:c>
+      <x:c r="R67" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S67" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="64" customHeight="1">
+      <x:c r="A68" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B68" s="6" t="str">
+        <x:v>postdoctoral_research</x:v>
+      </x:c>
+      <x:c r="C68" s="6" t="str"/>
+      <x:c r="D68" s="6" t="str">
+        <x:v>圣母大学</x:v>
+      </x:c>
+      <x:c r="E68" s="6" t="str"/>
+      <x:c r="F68" s="6" t="str">
+        <x:v>2024-12</x:v>
+      </x:c>
+      <x:c r="G68" s="6" t="str"/>
+      <x:c r="H68" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="I68" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="J68" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K68" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L68" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M68" s="7" t="str"/>
+      <x:c r="N68" s="6" t="str"/>
+      <x:c r="O68" s="6" t="str">
+        <x:v>本人CV起2024.02，Hu导师CV称2023.12，起始月冲突留空，结束月依本人CV。</x:v>
+      </x:c>
+      <x:c r="P68" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q68" s="6" t="str">
+        <x:v>https://zyyan.top/assets/pdf/Resume_ZJU.pdf</x:v>
+      </x:c>
+      <x:c r="R68" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S68" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="64" customHeight="1">
+      <x:c r="A69" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B69" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C69" s="6" t="str">
+        <x:v>百人计划研究员</x:v>
+      </x:c>
+      <x:c r="D69" s="6" t="str">
+        <x:v>浙江大学集成电路学院</x:v>
+      </x:c>
+      <x:c r="E69" s="6" t="str"/>
+      <x:c r="F69" s="6" t="str"/>
+      <x:c r="G69" s="6" t="str"/>
+      <x:c r="H69" s="6" t="str"/>
+      <x:c r="I69" s="6" t="str"/>
+      <x:c r="J69" s="6" t="str"/>
+      <x:c r="K69" s="6" t="str"/>
+      <x:c r="L69" s="6" t="str"/>
+      <x:c r="M69" s="7" t="str"/>
+      <x:c r="N69" s="6" t="str"/>
+      <x:c r="O69" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P69" s="6" t="str"/>
+      <x:c r="Q69" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/jcdlxjzzjsyjs/list2.htm</x:v>
+      </x:c>
+      <x:c r="R69" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S69" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="64" customHeight="1">
+      <x:c r="A70" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B70" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C70" s="6" t="str">
+        <x:v>博士后</x:v>
+      </x:c>
+      <x:c r="D70" s="6" t="str">
+        <x:v>圣母大学</x:v>
+      </x:c>
+      <x:c r="E70" s="6" t="str"/>
+      <x:c r="F70" s="6" t="str">
+        <x:v>2024-12</x:v>
+      </x:c>
+      <x:c r="G70" s="6" t="str"/>
+      <x:c r="H70" s="6" t="str"/>
+      <x:c r="I70" s="6" t="str"/>
+      <x:c r="J70" s="6" t="str"/>
+      <x:c r="K70" s="6" t="str"/>
+      <x:c r="L70" s="6" t="str"/>
+      <x:c r="M70" s="7" t="str"/>
+      <x:c r="N70" s="6" t="str"/>
+      <x:c r="O70" s="6" t="str">
+        <x:v>起始2024.02与Hu2023.12冲突；与博士结束时间重叠不自行更改。</x:v>
+      </x:c>
+      <x:c r="P70" s="6" t="str"/>
+      <x:c r="Q70" s="6" t="str">
+        <x:v>https://zyyan.top/assets/pdf/Resume_ZJU.pdf</x:v>
+      </x:c>
+      <x:c r="R70" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S70" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="64" customHeight="1">
+      <x:c r="A71" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B71" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C71" s="6" t="str">
+        <x:v>百人计划研究员（Assistant Professor）</x:v>
+      </x:c>
+      <x:c r="D71" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+      <x:c r="E71" s="6" t="str">
+        <x:v>2025-01</x:v>
+      </x:c>
+      <x:c r="F71" s="6" t="str"/>
+      <x:c r="G71" s="6" t="str"/>
+      <x:c r="H71" s="6" t="str"/>
+      <x:c r="I71" s="6" t="str"/>
+      <x:c r="J71" s="6" t="str"/>
+      <x:c r="K71" s="6" t="str"/>
+      <x:c r="L71" s="6" t="str"/>
+      <x:c r="M71" s="7" t="str"/>
+      <x:c r="N71" s="6" t="str"/>
+      <x:c r="O71" s="6" t="str"/>
+      <x:c r="P71" s="6" t="str"/>
+      <x:c r="Q71" s="6" t="str">
+        <x:v>https://zyyan.top/assets/pdf/Resume_ZJU.pdf</x:v>
+      </x:c>
+      <x:c r="R71" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="S71" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d6fbc04558f4f4e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re06484c8d4764930"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2978,8 +4051,277 @@
         <x:v>所属学校</x:v>
       </x:c>
     </x:row>
+    <x:row r="2" ht="64" customHeight="1">
+      <x:c r="A2" s="6" t="str">
+        <x:v>孙奇</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>Bei Yu</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>博士导师</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str">
+        <x:v>香港中文大学计算机科学与工程系教授，研究EDA与机器学习。</x:v>
+      </x:c>
+      <x:c r="F2" s="6" t="str">
+        <x:v>active_officially_listed</x:v>
+      </x:c>
+      <x:c r="G2" s="6" t="str">
+        <x:v>官方教师页当前列示教授，不独立核人事在岗。</x:v>
+      </x:c>
+      <x:c r="H2" s="6" t="str">
+        <x:v>https://www.cse.cuhk.edu.hk/~byu/</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str">
+        <x:v>https://qisunchn.top/index.html</x:v>
+      </x:c>
+      <x:c r="J2" s="6" t="str">
+        <x:v>https://www.cse.cuhk.edu.hk/~byu/</x:v>
+      </x:c>
+      <x:c r="K2" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="L2" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="64" customHeight="1">
+      <x:c r="A3" s="6" t="str">
+        <x:v>孙奇</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="str">
+        <x:v>Zhiru Zhang</x:v>
+      </x:c>
+      <x:c r="C3" s="6" t="str">
+        <x:v>博士后合作导师（非博士授位导师）</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="str">
+        <x:v>博士后</x:v>
+      </x:c>
+      <x:c r="E3" s="6" t="str">
+        <x:v>康奈尔大学电气与计算机工程学院教授，研究异构计算与EDA。</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="str">
+        <x:v>active_officially_listed</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="str">
+        <x:v>官方教师页当前列示教授，不独立核人事在岗。</x:v>
+      </x:c>
+      <x:c r="H3" s="6" t="str">
+        <x:v>https://www.csl.cornell.edu/~zhiruz/</x:v>
+      </x:c>
+      <x:c r="I3" s="6" t="str">
+        <x:v>https://qisunchn.top/experience.html</x:v>
+      </x:c>
+      <x:c r="J3" s="6" t="str">
+        <x:v>https://www.csl.cornell.edu/~zhiruz/</x:v>
+      </x:c>
+      <x:c r="K3" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="L3" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="64" customHeight="1">
+      <x:c r="A4" s="6" t="str">
+        <x:v>李骏康</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="str">
+        <x:v>张睿</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="str">
+        <x:v>博士导师</x:v>
+      </x:c>
+      <x:c r="D4" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E4" s="6" t="str">
+        <x:v>浙江大学集成电路学院教授，研究新沟道材料场效应晶体管与器件物理。</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="str">
+        <x:v>active_officially_listed</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="str">
+        <x:v>学院当前名录及本人页列示教授。</x:v>
+      </x:c>
+      <x:c r="H4" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/0012183</x:v>
+      </x:c>
+      <x:c r="I4" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/2020/1220/c53675a2235682/page.htm</x:v>
+      </x:c>
+      <x:c r="J4" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/0012183</x:v>
+      </x:c>
+      <x:c r="K4" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="L4" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="64" customHeight="1">
+      <x:c r="A5" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="str">
+        <x:v>Yiyu Shi</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="str">
+        <x:v>博士联合导师</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E5" s="6" t="str">
+        <x:v>圣母大学计算机科学与工程教授，研究深度学习硬件软件协同设计。</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="str">
+        <x:v>active_officially_listed</x:v>
+      </x:c>
+      <x:c r="G5" s="6" t="str">
+        <x:v>官方教授页面当前列示。</x:v>
+      </x:c>
+      <x:c r="H5" s="6" t="str">
+        <x:v>https://engineering.nd.edu/faculty/yiyu-shi/</x:v>
+      </x:c>
+      <x:c r="I5" s="6" t="str">
+        <x:v>https://sites.nd.edu/zheyu-yan/</x:v>
+      </x:c>
+      <x:c r="J5" s="6" t="str">
+        <x:v>https://engineering.nd.edu/faculty/yiyu-shi/</x:v>
+      </x:c>
+      <x:c r="K5" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="L5" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="64" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="str">
+        <x:v>Xiaobo Sharon Hu</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="str">
+        <x:v>博士联合导师</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str">
+        <x:v>圣母大学工程学讲席教授，研究计算架构及系统可靠性。</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="str">
+        <x:v>active_officially_listed</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="str">
+        <x:v>官方教授页面当前列示。</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="str">
+        <x:v>https://sites.nd.edu/xsharon-hu/</x:v>
+      </x:c>
+      <x:c r="I6" s="6" t="str">
+        <x:v>https://sites.nd.edu/zheyu-yan/</x:v>
+      </x:c>
+      <x:c r="J6" s="6" t="str">
+        <x:v>https://sites.nd.edu/xsharon-hu/</x:v>
+      </x:c>
+      <x:c r="K6" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="L6" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="64" customHeight="1">
+      <x:c r="A7" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="str">
+        <x:v>Yiyu Shi</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="str">
+        <x:v>博士后合作导师（非博士授位导师）</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>博士后</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="str">
+        <x:v>圣母大学计算机科学与工程教授。</x:v>
+      </x:c>
+      <x:c r="F7" s="6" t="str">
+        <x:v>active_officially_listed</x:v>
+      </x:c>
+      <x:c r="G7" s="6" t="str">
+        <x:v>官方教授页面当前列示。</x:v>
+      </x:c>
+      <x:c r="H7" s="6" t="str">
+        <x:v>https://engineering.nd.edu/faculty/yiyu-shi/</x:v>
+      </x:c>
+      <x:c r="I7" s="6" t="str">
+        <x:v>https://zyyan.top/assets/pdf/Resume_ZJU.pdf</x:v>
+      </x:c>
+      <x:c r="J7" s="6" t="str">
+        <x:v>https://engineering.nd.edu/faculty/yiyu-shi/</x:v>
+      </x:c>
+      <x:c r="K7" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="L7" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="64" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>Xiaobo Sharon Hu</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str">
+        <x:v>博士后合作导师（非博士授位导师）</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>博士后</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="str">
+        <x:v>圣母大学工程学讲席教授。</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="str">
+        <x:v>active_officially_listed</x:v>
+      </x:c>
+      <x:c r="G8" s="6" t="str">
+        <x:v>官方教授页面当前列示。</x:v>
+      </x:c>
+      <x:c r="H8" s="6" t="str">
+        <x:v>https://sites.nd.edu/xsharon-hu/</x:v>
+      </x:c>
+      <x:c r="I8" s="6" t="str">
+        <x:v>https://sites.nd.edu/xsharon-hu/files/2024/08/web.pdf</x:v>
+      </x:c>
+      <x:c r="J8" s="6" t="str">
+        <x:v>https://sites.nd.edu/xsharon-hu/</x:v>
+      </x:c>
+      <x:c r="K8" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="L8" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d2740db195a4040"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
@@ -3187,10 +4529,82 @@
         <x:v>浙江大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="6" ht="64" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="str">
+        <x:v>U-SWIM: Universal Selective Write-Verify for Computing-in-Memory Neural Accelerators</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str"/>
+      <x:c r="E6" s="6" t="str">
+        <x:v>https://sites.nd.edu/zheyu-yan/</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="str">
+        <x:v>https://sites.nd.edu/zheyu-yan/</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/zyan2</x:v>
+      </x:c>
+      <x:c r="I6" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J6" s="6" t="str">
+        <x:v>ND本人页精选书目，未逐篇出版链接。</x:v>
+      </x:c>
+      <x:c r="K6" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="L6" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="64" customHeight="1">
+      <x:c r="A7" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="str">
+        <x:v>Compute-in-Memory based Neural Network Accelerators for Safety-Critical Systems: Worst-Case Scenarios and Protections</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>https://sites.nd.edu/zheyu-yan/</x:v>
+      </x:c>
+      <x:c r="F7" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G7" s="6" t="str">
+        <x:v>https://sites.nd.edu/zheyu-yan/</x:v>
+      </x:c>
+      <x:c r="H7" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/zyan2</x:v>
+      </x:c>
+      <x:c r="I7" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J7" s="6" t="str">
+        <x:v>ND本人页精选书目，未逐篇出版链接。</x:v>
+      </x:c>
+      <x:c r="K7" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="L7" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e316a248ab24e06"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5dcf323e944d4925"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3923,16 +5337,16 @@
     </x:row>
     <x:row r="32" ht="64" customHeight="1">
       <x:c r="A32" s="6" t="str">
-        <x:v>綦殿禹</x:v>
+        <x:v>张运炎</x:v>
       </x:c>
       <x:c r="B32" s="6" t="str">
-        <x:v>institution-classification-2</x:v>
+        <x:v>zhangyunyan-source-1</x:v>
       </x:c>
       <x:c r="C32" s="6" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+        <x:v>https://ic.zju.edu.cn/jcdlxjzzjsyjs/list2.htm</x:v>
       </x:c>
       <x:c r="D32" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_roster_read</x:v>
       </x:c>
       <x:c r="E32" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -3946,16 +5360,16 @@
     </x:row>
     <x:row r="33" ht="64" customHeight="1">
       <x:c r="A33" s="6" t="str">
-        <x:v>程志渊</x:v>
+        <x:v>张运炎</x:v>
       </x:c>
       <x:c r="B33" s="6" t="str">
-        <x:v>institution-classification-4</x:v>
+        <x:v>zhangyunyan-source-2</x:v>
       </x:c>
       <x:c r="C33" s="6" t="str">
-        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+        <x:v>https://optics.iphy.ac.cn/detail.php?id=29448</x:v>
       </x:c>
       <x:c r="D33" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
       <x:c r="E33" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -3969,16 +5383,16 @@
     </x:row>
     <x:row r="34" ht="64" customHeight="1">
       <x:c r="A34" s="6" t="str">
-        <x:v>程志渊</x:v>
+        <x:v>张运炎</x:v>
       </x:c>
       <x:c r="B34" s="6" t="str">
-        <x:v>institution-classification-5</x:v>
+        <x:v>zhangyunyan-source-3</x:v>
       </x:c>
       <x:c r="C34" s="6" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+        <x:v>https://www.nanomat-conference.com/uploads/9/6/6/5/96656038/booklet_nanomat2018.pdf</x:v>
       </x:c>
       <x:c r="D34" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
       <x:c r="E34" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -3992,16 +5406,16 @@
     </x:row>
     <x:row r="35" ht="64" customHeight="1">
       <x:c r="A35" s="6" t="str">
-        <x:v>卓成</x:v>
+        <x:v>张运炎</x:v>
       </x:c>
       <x:c r="B35" s="6" t="str">
-        <x:v>institution-classification-6</x:v>
+        <x:v>zhangyunyan-source-4</x:v>
       </x:c>
       <x:c r="C35" s="6" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+        <x:v>https://hr.zju.edu.cn/postdoctor/2022/0427/c29115a2524719/page.htm</x:v>
       </x:c>
       <x:c r="D35" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
       <x:c r="E35" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -4015,16 +5429,16 @@
     </x:row>
     <x:row r="36" ht="64" customHeight="1">
       <x:c r="A36" s="6" t="str">
-        <x:v>韩雁</x:v>
+        <x:v>孙奇</x:v>
       </x:c>
       <x:c r="B36" s="6" t="str">
-        <x:v>institution-classification-2</x:v>
+        <x:v>sunqi-source-1</x:v>
       </x:c>
       <x:c r="C36" s="6" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+        <x:v>https://ic.zju.edu.cn/jcdlxjzzjsyjs/list2.htm</x:v>
       </x:c>
       <x:c r="D36" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_roster_read</x:v>
       </x:c>
       <x:c r="E36" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -4038,16 +5452,16 @@
     </x:row>
     <x:row r="37" ht="64" customHeight="1">
       <x:c r="A37" s="6" t="str">
-        <x:v>张睿</x:v>
+        <x:v>孙奇</x:v>
       </x:c>
       <x:c r="B37" s="6" t="str">
-        <x:v>institution-classification-3</x:v>
+        <x:v>sunqi-source-2</x:v>
       </x:c>
       <x:c r="C37" s="6" t="str">
-        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+        <x:v>https://qisunchn.top/index.html</x:v>
       </x:c>
       <x:c r="D37" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>本人自述职业网站（已有官方身份交叉核验，非学校域名官网）；self_reported_professional_website_identity_cross_checked</x:v>
       </x:c>
       <x:c r="E37" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -4061,31 +5475,606 @@
     </x:row>
     <x:row r="38" ht="64" customHeight="1">
       <x:c r="A38" s="6" t="str">
+        <x:v>孙奇</x:v>
+      </x:c>
+      <x:c r="B38" s="6" t="str">
+        <x:v>sunqi-source-3</x:v>
+      </x:c>
+      <x:c r="C38" s="6" t="str">
+        <x:v>https://qisunchn.top/experience.html</x:v>
+      </x:c>
+      <x:c r="D38" s="6" t="str">
+        <x:v>本人自述职业网站（已有官方身份交叉核验，非学校域名官网）；self_reported_professional_website_identity_cross_checked</x:v>
+      </x:c>
+      <x:c r="E38" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F38" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G38" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="64" customHeight="1">
+      <x:c r="A39" s="6" t="str">
+        <x:v>孙奇</x:v>
+      </x:c>
+      <x:c r="B39" s="6" t="str">
+        <x:v>sunqi-source-4</x:v>
+      </x:c>
+      <x:c r="C39" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/0023146</x:v>
+      </x:c>
+      <x:c r="D39" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E39" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F39" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G39" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="64" customHeight="1">
+      <x:c r="A40" s="6" t="str">
+        <x:v>孙奇</x:v>
+      </x:c>
+      <x:c r="B40" s="6" t="str">
+        <x:v>sunqi-source-5</x:v>
+      </x:c>
+      <x:c r="C40" s="6" t="str">
+        <x:v>https://www.cse.cuhk.edu.hk/~byu/</x:v>
+      </x:c>
+      <x:c r="D40" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E40" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F40" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G40" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="64" customHeight="1">
+      <x:c r="A41" s="6" t="str">
+        <x:v>孙奇</x:v>
+      </x:c>
+      <x:c r="B41" s="6" t="str">
+        <x:v>sunqi-source-6</x:v>
+      </x:c>
+      <x:c r="C41" s="6" t="str">
+        <x:v>https://www.csl.cornell.edu/~zhiruz/</x:v>
+      </x:c>
+      <x:c r="D41" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E41" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F41" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G41" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="64" customHeight="1">
+      <x:c r="A42" s="6" t="str">
+        <x:v>李骏康</x:v>
+      </x:c>
+      <x:c r="B42" s="6" t="str">
+        <x:v>lijunkang-source-1</x:v>
+      </x:c>
+      <x:c r="C42" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/jcdlxjzzjsyjs/list2.htm</x:v>
+      </x:c>
+      <x:c r="D42" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E42" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F42" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G42" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="64" customHeight="1">
+      <x:c r="A43" s="6" t="str">
+        <x:v>李骏康</x:v>
+      </x:c>
+      <x:c r="B43" s="6" t="str">
+        <x:v>lijunkang-source-2</x:v>
+      </x:c>
+      <x:c r="C43" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/2020/1220/c53675a2235682/page.htm</x:v>
+      </x:c>
+      <x:c r="D43" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E43" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F43" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G43" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="64" customHeight="1">
+      <x:c r="A44" s="6" t="str">
+        <x:v>李骏康</x:v>
+      </x:c>
+      <x:c r="B44" s="6" t="str">
+        <x:v>lijunkang-source-3</x:v>
+      </x:c>
+      <x:c r="C44" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/JunkangLi</x:v>
+      </x:c>
+      <x:c r="D44" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E44" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F44" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G44" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="64" customHeight="1">
+      <x:c r="A45" s="6" t="str">
+        <x:v>李骏康</x:v>
+      </x:c>
+      <x:c r="B45" s="6" t="str">
+        <x:v>lijunkang-source-4</x:v>
+      </x:c>
+      <x:c r="C45" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/0012183</x:v>
+      </x:c>
+      <x:c r="D45" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E45" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F45" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G45" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="64" customHeight="1">
+      <x:c r="A46" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B46" s="6" t="str">
+        <x:v>yanzheyu-source-1</x:v>
+      </x:c>
+      <x:c r="C46" s="6" t="str">
+        <x:v>https://ic.zju.edu.cn/jcdlxjzzjsyjs/list2.htm</x:v>
+      </x:c>
+      <x:c r="D46" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E46" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F46" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G46" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="64" customHeight="1">
+      <x:c r="A47" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B47" s="6" t="str">
+        <x:v>yanzheyu-source-2</x:v>
+      </x:c>
+      <x:c r="C47" s="6" t="str">
+        <x:v>https://sites.nd.edu/zheyu-yan/</x:v>
+      </x:c>
+      <x:c r="D47" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E47" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F47" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G47" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="64" customHeight="1">
+      <x:c r="A48" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B48" s="6" t="str">
+        <x:v>yanzheyu-source-3</x:v>
+      </x:c>
+      <x:c r="C48" s="6" t="str">
+        <x:v>https://zyyan.top/assets/pdf/Resume_ZJU.pdf</x:v>
+      </x:c>
+      <x:c r="D48" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E48" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F48" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G48" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="64" customHeight="1">
+      <x:c r="A49" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B49" s="6" t="str">
+        <x:v>yanzheyu-source-4</x:v>
+      </x:c>
+      <x:c r="C49" s="6" t="str">
+        <x:v>https://sites.nd.edu/xsharon-hu/files/2024/08/web.pdf</x:v>
+      </x:c>
+      <x:c r="D49" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E49" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F49" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G49" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="64" customHeight="1">
+      <x:c r="A50" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B50" s="6" t="str">
+        <x:v>yanzheyu-source-5</x:v>
+      </x:c>
+      <x:c r="C50" s="6" t="str">
+        <x:v>https://commencement.nd.edu/assets/569412/program_2024_official.pdf</x:v>
+      </x:c>
+      <x:c r="D50" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E50" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F50" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G50" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="64" customHeight="1">
+      <x:c r="A51" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B51" s="6" t="str">
+        <x:v>yanzheyu-source-6</x:v>
+      </x:c>
+      <x:c r="C51" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/zyan2</x:v>
+      </x:c>
+      <x:c r="D51" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E51" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F51" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G51" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="64" customHeight="1">
+      <x:c r="A52" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B52" s="6" t="str">
+        <x:v>yanzheyu-source-7</x:v>
+      </x:c>
+      <x:c r="C52" s="6" t="str">
+        <x:v>https://engineering.nd.edu/faculty/yiyu-shi/</x:v>
+      </x:c>
+      <x:c r="D52" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E52" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F52" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G52" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="64" customHeight="1">
+      <x:c r="A53" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B53" s="6" t="str">
+        <x:v>yanzheyu-source-8</x:v>
+      </x:c>
+      <x:c r="C53" s="6" t="str">
+        <x:v>https://sites.nd.edu/xsharon-hu/</x:v>
+      </x:c>
+      <x:c r="D53" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E53" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F53" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G53" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="64" customHeight="1">
+      <x:c r="A54" s="6" t="str">
+        <x:v>綦殿禹</x:v>
+      </x:c>
+      <x:c r="B54" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C54" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D54" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E54" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F54" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G54" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="64" customHeight="1">
+      <x:c r="A55" s="6" t="str">
+        <x:v>程志渊</x:v>
+      </x:c>
+      <x:c r="B55" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C55" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D55" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E55" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F55" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G55" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="64" customHeight="1">
+      <x:c r="A56" s="6" t="str">
+        <x:v>程志渊</x:v>
+      </x:c>
+      <x:c r="B56" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C56" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D56" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E56" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F56" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G56" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="64" customHeight="1">
+      <x:c r="A57" s="6" t="str">
+        <x:v>卓成</x:v>
+      </x:c>
+      <x:c r="B57" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C57" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D57" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E57" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F57" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G57" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="64" customHeight="1">
+      <x:c r="A58" s="6" t="str">
+        <x:v>韩雁</x:v>
+      </x:c>
+      <x:c r="B58" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C58" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D58" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E58" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F58" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G58" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="64" customHeight="1">
+      <x:c r="A59" s="6" t="str">
         <x:v>张睿</x:v>
       </x:c>
-      <x:c r="B38" s="6" t="str">
+      <x:c r="B59" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C59" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D59" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E59" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F59" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G59" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="64" customHeight="1">
+      <x:c r="A60" s="6" t="str">
+        <x:v>张睿</x:v>
+      </x:c>
+      <x:c r="B60" s="6" t="str">
         <x:v>institution-classification-4</x:v>
       </x:c>
-      <x:c r="C38" s="6" t="str">
+      <x:c r="C60" s="6" t="str">
         <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
       </x:c>
-      <x:c r="D38" s="6" t="str">
+      <x:c r="D60" s="6" t="str">
         <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
       </x:c>
-      <x:c r="E38" s="7" t="d">
-        <x:v>2026-10-23T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="F38" s="6" t="str">
-        <x:v>zju</x:v>
-      </x:c>
-      <x:c r="G38" s="6" t="str">
+      <x:c r="E60" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F60" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G60" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="64" customHeight="1">
+      <x:c r="A61" s="6" t="str">
+        <x:v>孙奇</x:v>
+      </x:c>
+      <x:c r="B61" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C61" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D61" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E61" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F61" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G61" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="64" customHeight="1">
+      <x:c r="A62" s="6" t="str">
+        <x:v>李骏康</x:v>
+      </x:c>
+      <x:c r="B62" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C62" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D62" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E62" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F62" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G62" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="64" customHeight="1">
+      <x:c r="A63" s="6" t="str">
+        <x:v>严哲雨</x:v>
+      </x:c>
+      <x:c r="B63" s="6" t="str">
+        <x:v>institution-classification-8</x:v>
+      </x:c>
+      <x:c r="C63" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D63" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E63" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F63" s="6" t="str">
+        <x:v>zju</x:v>
+      </x:c>
+      <x:c r="G63" s="6" t="str">
         <x:v>浙江大学</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14d9f4f5885048ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2ae1f27ded6422d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/zju-ic-manufacturing.xlsx
+++ b/site/exports/zju-ic-manufacturing.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R067c829f947041b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Rbaed432908ef4fca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rd6bbf00e635a4b25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Rd248767c691a4da9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R221e5ce5e78b4e27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rc84bda3cfb2b4000"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R3423d11a273441b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R74b02c0a1f1f425a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Rfaacd94f0349469e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R3461e6e2f83c4918"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T10_0" displayName="T10_0" ref="A1:K14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T14_0" displayName="T14_0" ref="A1:K14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T10_1" displayName="T10_1" ref="A1:S71" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T14_1" displayName="T14_1" ref="A1:S71" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -185,7 +185,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T10_2" displayName="T10_2" ref="A1:L8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T14_2" displayName="T14_2" ref="A1:L8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="导师姓名"/>
@@ -205,7 +205,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T10_3" displayName="T10_3" ref="A1:L7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T14_3" displayName="T14_3" ref="A1:L7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T10_4" displayName="T10_4" ref="A1:G63" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T14_4" displayName="T14_4" ref="A1:G63" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -914,7 +914,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re039f7ebbdd34140"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb0cc0112bac4fdc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3990,7 +3990,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re06484c8d4764930"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d1432bb7b6c4cbd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4320,7 +4320,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d2740db195a4040"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6178eafebc5242d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4396,7 +4396,7 @@
         <x:v>https://pi.zju.edu.cn/2022/0711/c68814a2603352/page.psp</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G2" s="6" t="str">
         <x:v>https://pi.zju.edu.cn/2022/0711/c68814a2603352/page.psp</x:v>
@@ -4405,7 +4405,7 @@
         <x:v>https://person.zju.edu.cn/chengzhuo</x:v>
       </x:c>
       <x:c r="I2" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J2" s="6" t="str">
         <x:v>工程师学院本人项目制导师栏目精选，未逐篇出版者链接。</x:v>
@@ -4432,7 +4432,7 @@
         <x:v>https://pi.zju.edu.cn/2022/0711/c68814a2603352/page.psp</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G3" s="6" t="str">
         <x:v>https://pi.zju.edu.cn/2022/0711/c68814a2603352/page.psp</x:v>
@@ -4441,7 +4441,7 @@
         <x:v>https://person.zju.edu.cn/chengzhuo</x:v>
       </x:c>
       <x:c r="I3" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J3" s="6" t="str">
         <x:v>工程师学院本人项目制导师栏目精选，未逐篇出版者链接。</x:v>
@@ -4470,7 +4470,7 @@
         <x:v>https://www.jos.ac.cn/article/id/5fac63df-cd6c-47dc-94ea-fe4e93ea190c?viewType=HTML</x:v>
       </x:c>
       <x:c r="F4" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G4" s="6" t="str">
         <x:v>https://www.jos.ac.cn/article/id/5fac63df-cd6c-47dc-94ea-fe4e93ea190c?viewType=HTML</x:v>
@@ -4479,7 +4479,7 @@
         <x:v>https://person.zju.edu.cn/0012183</x:v>
       </x:c>
       <x:c r="I4" s="6" t="str">
-        <x:v>article_metadata_verified</x:v>
+        <x:v>单篇文章书目元数据已核，不表示成果全集或全文复制。；article_metadata_verified</x:v>
       </x:c>
       <x:c r="J4" s="6" t="str">
         <x:v>正式出版者正文作者简介同时提供教育证据；仅精选一篇，不从共同作者推导师。</x:v>
@@ -4508,7 +4508,7 @@
         <x:v>https://www.jos.ac.cn/article/id/5fac63df-cd6c-47dc-94ea-fe4e93ea190c?viewType=HTML</x:v>
       </x:c>
       <x:c r="F5" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G5" s="6" t="str">
         <x:v>https://www.jos.ac.cn/article/id/5fac63df-cd6c-47dc-94ea-fe4e93ea190c?viewType=HTML</x:v>
@@ -4517,7 +4517,7 @@
         <x:v>https://person.zju.edu.cn/chengran</x:v>
       </x:c>
       <x:c r="I5" s="6" t="str">
-        <x:v>article_metadata_verified</x:v>
+        <x:v>单篇文章书目元数据已核，不表示成果全集或全文复制。；article_metadata_verified</x:v>
       </x:c>
       <x:c r="J5" s="6" t="str">
         <x:v>正式出版者全文作者简介；第一作者Ran Cheng的NUS/浙江大学半导体专业身份与此前官方讲座一致，排除香港理工AI同名人。</x:v>
@@ -4544,7 +4544,7 @@
         <x:v>https://sites.nd.edu/zheyu-yan/</x:v>
       </x:c>
       <x:c r="F6" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G6" s="6" t="str">
         <x:v>https://sites.nd.edu/zheyu-yan/</x:v>
@@ -4553,7 +4553,7 @@
         <x:v>https://person.zju.edu.cn/zyan2</x:v>
       </x:c>
       <x:c r="I6" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J6" s="6" t="str">
         <x:v>ND本人页精选书目，未逐篇出版链接。</x:v>
@@ -4580,7 +4580,7 @@
         <x:v>https://sites.nd.edu/zheyu-yan/</x:v>
       </x:c>
       <x:c r="F7" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G7" s="6" t="str">
         <x:v>https://sites.nd.edu/zheyu-yan/</x:v>
@@ -4589,7 +4589,7 @@
         <x:v>https://person.zju.edu.cn/zyan2</x:v>
       </x:c>
       <x:c r="I7" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J7" s="6" t="str">
         <x:v>ND本人页精选书目，未逐篇出版链接。</x:v>
@@ -4604,7 +4604,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5dcf323e944d4925"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1f5a37da028467b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6074,7 +6074,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2ae1f27ded6422d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5183642495e749e2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/zju-ic-manufacturing.xlsx
+++ b/site/exports/zju-ic-manufacturing.xlsx
@@ -452,8 +452,8 @@
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="18.2" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="37.8" customWidth="1" min="7" max="7"/>
+    <col width="26.6" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -655,12 +655,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -708,12 +708,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -761,12 +761,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -814,12 +814,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -867,12 +867,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -920,12 +920,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -973,12 +973,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
